--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-24).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-24).xlsx
@@ -912,66 +912,66 @@
   </si>
   <si>
     <t>214
-126</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>R$ 618.316,85</t>
-  </si>
-  <si>
-    <t>R$ 4.719,98
-R$ 4.783,22</t>
-  </si>
-  <si>
-    <t>(13.3%)
-(12.2%)</t>
-  </si>
-  <si>
-    <t>52.2</t>
-  </si>
-  <si>
-    <t>(12.8%)</t>
-  </si>
-  <si>
-    <t>(650.5%)</t>
-  </si>
-  <si>
-    <t>(693.4%)</t>
-  </si>
-  <si>
-    <t>3.3%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>25.9</t>
-  </si>
-  <si>
-    <t>70.7%</t>
-  </si>
-  <si>
-    <t>7.7%</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>6.6</t>
-  </si>
-  <si>
-    <t>11.3</t>
-  </si>
-  <si>
-    <t>17.9</t>
-  </si>
-  <si>
-    <t>75.2%</t>
-  </si>
-  <si>
-    <t>-R$ 16.942,15</t>
+175</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 855.602,66</t>
+  </si>
+  <si>
+    <t>R$ 4.650,01
+R$ 4.706,95</t>
+  </si>
+  <si>
+    <t>(14.6%)
+(13.5%)</t>
+  </si>
+  <si>
+    <t>51.2</t>
+  </si>
+  <si>
+    <t>(14.7%)</t>
+  </si>
+  <si>
+    <t>(463.7%)</t>
+  </si>
+  <si>
+    <t>(506.9%)</t>
+  </si>
+  <si>
+    <t>3.9%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>26.2</t>
+  </si>
+  <si>
+    <t>70.2%</t>
+  </si>
+  <si>
+    <t>7.9%</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>6.7</t>
+  </si>
+  <si>
+    <t>11.6</t>
+  </si>
+  <si>
+    <t>18.2</t>
+  </si>
+  <si>
+    <t>74.1%</t>
+  </si>
+  <si>
+    <t>-R$ 21.077,20</t>
   </si>
   <si>
     <t>2.95</t>
@@ -1806,7 +1806,7 @@
         <v>19505</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C4" s="4">
         <v>44</v>
@@ -1842,27 +1842,61 @@
       <c t="s" r="N4" s="4">
         <v>52</v>
       </c>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="8"/>
-      <c r="AB4" s="8"/>
+      <c r="O4" s="5">
+        <v>6914.2600000000002</v>
+      </c>
+      <c r="P4" s="5">
+        <v>6914.2600000000002</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>0.50498450233335657</v>
+      </c>
+      <c r="R4" s="7">
+        <v>73</v>
+      </c>
+      <c r="S4" s="6">
+        <v>0.21666666666666656</v>
+      </c>
+      <c r="T4" s="6">
+        <v>0.29147881335095877</v>
+      </c>
+      <c r="U4" s="6">
+        <v>-0.024847156456366985</v>
+      </c>
+      <c r="V4" s="6">
+        <v>0.030416704029064569</v>
+      </c>
+      <c r="W4" s="6">
+        <v>-0.013320442100817729</v>
+      </c>
+      <c r="X4" s="8">
+        <v>23.415722641509436</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="Z4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="8">
+        <v>6.3387323943661977</v>
+      </c>
+      <c r="AB4" s="8">
+        <v>5.1635226415094335</v>
+      </c>
       <c r="AC4" s="8">
-        <v>12.118952999999999</v>
-      </c>
-      <c r="AD4" s="8"/>
-      <c r="AE4" s="6"/>
+        <v>12.035534</v>
+      </c>
+      <c r="AD4" s="8">
+        <v>17.262264150943395</v>
+      </c>
+      <c r="AE4" s="6">
+        <v>0.81132075471698117</v>
+      </c>
       <c r="AF4" s="9"/>
-      <c r="AG4" s="5"/>
+      <c r="AG4" s="5">
+        <v>-65.799999999999997</v>
+      </c>
       <c r="AH4" s="10">
         <v>5</v>
       </c>
@@ -2179,10 +2213,10 @@
         <v>-0.042253521126760618</v>
       </c>
       <c r="T7" s="6">
-        <v>0.36174548034931747</v>
+        <v>0.38282604456176156</v>
       </c>
       <c r="U7" s="6">
-        <v>-0.017429589824951214</v>
+        <v>0.003650974387492813</v>
       </c>
       <c r="V7" s="6">
         <v>0.03217133215988284</v>
@@ -2205,7 +2239,9 @@
       <c r="AB7" s="8">
         <v>5.2442718749999999</v>
       </c>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="8">
+        <v>20.703793000000001</v>
+      </c>
       <c r="AD7" s="8">
         <v>26.258332352941178</v>
       </c>
@@ -2310,10 +2346,10 @@
         <v>-0.27848101265822789</v>
       </c>
       <c r="T8" s="6">
-        <v>0.33833726203974457</v>
+        <v>0.3500311809989855</v>
       </c>
       <c r="U8" s="6">
-        <v>0.008530528819512528</v>
+        <v>0.020224447778753443</v>
       </c>
       <c r="V8" s="6">
         <v>0.047272461828319082</v>
@@ -2649,7 +2685,7 @@
         <v>19513</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C11" s="4">
         <v>44</v>
@@ -2685,25 +2721,61 @@
       <c t="s" r="N11" s="4">
         <v>52</v>
       </c>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="8"/>
-      <c r="AE11" s="6"/>
+      <c r="O11" s="5">
+        <v>6446.6599999999999</v>
+      </c>
+      <c r="P11" s="5">
+        <v>6446.6599999999999</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>-0.27702009355384627</v>
+      </c>
+      <c r="R11" s="7">
+        <v>63</v>
+      </c>
+      <c r="S11" s="6">
+        <v>-0.31521739130434778</v>
+      </c>
+      <c r="T11" s="6">
+        <v>0.34068834093933914</v>
+      </c>
+      <c r="U11" s="6">
+        <v>0.048869011239928893</v>
+      </c>
+      <c r="V11" s="6">
+        <v>0.028919471478253855</v>
+      </c>
+      <c r="W11" s="6">
+        <v>0.0068677423658142361</v>
+      </c>
+      <c r="X11" s="8">
+        <v>23.968699999999998</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>0.70731707317073167</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="8">
+        <v>5.0190854838709678</v>
+      </c>
+      <c r="AB11" s="8">
+        <v>3.2747975609756095</v>
+      </c>
+      <c r="AC11" s="8">
+        <v>8.9296740000000003</v>
+      </c>
+      <c r="AD11" s="8">
+        <v>14.872763414634148</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>0.82926829268292679</v>
+      </c>
       <c r="AF11" s="9"/>
-      <c r="AG11" s="5"/>
+      <c r="AG11" s="5">
+        <v>0</v>
+      </c>
       <c r="AH11" s="10">
         <v>3</v>
       </c>
@@ -2875,7 +2947,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2911,25 +2983,61 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="O13" s="5">
+        <v>7453.8000000000002</v>
+      </c>
+      <c r="P13" s="5">
+        <v>7453.8000000000002</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>-0.12114059062257543</v>
+      </c>
+      <c r="R13" s="7">
+        <v>80</v>
+      </c>
+      <c r="S13" s="6">
+        <v>-0.101123595505618</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.50044781185435616</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0.18450292468271218</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.0273372642142263</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.00082461294909978798</v>
+      </c>
+      <c r="X13" s="8">
+        <v>28.743000000000002</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.64000000000000001</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>6.0044871794871799</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>7.190334</v>
+      </c>
+      <c r="AC13" s="8">
+        <v>13.223333</v>
+      </c>
+      <c r="AD13" s="8">
+        <v>20.169665999999999</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>-41.899999999999999</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -3101,7 +3209,7 @@
         <v>19519</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C15" s="4">
         <v>44</v>
@@ -3137,25 +3245,61 @@
       <c t="s" r="N15" s="4">
         <v>52</v>
       </c>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="8"/>
-      <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
-      <c r="AD15" s="8"/>
-      <c r="AE15" s="6"/>
+      <c r="O15" s="5">
+        <v>14000.030000000001</v>
+      </c>
+      <c r="P15" s="5">
+        <v>14000.030000000001</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>-0.067908077291559676</v>
+      </c>
+      <c r="R15" s="7">
+        <v>162</v>
+      </c>
+      <c r="S15" s="6">
+        <v>-0.029940119760479056</v>
+      </c>
+      <c r="T15" s="6">
+        <v>0.33549658822159667</v>
+      </c>
+      <c r="U15" s="6">
+        <v>0.021119404744132691</v>
+      </c>
+      <c r="V15" s="6">
+        <v>0.025192981729324864</v>
+      </c>
+      <c r="W15" s="6">
+        <v>0.0058780231185218889</v>
+      </c>
+      <c r="X15" s="8">
+        <v>21.908450704225352</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>0.94366197183098588</v>
+      </c>
+      <c r="Z15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="8">
+        <v>4.185683974358974</v>
+      </c>
+      <c r="AB15" s="8">
+        <v>4.0254757142857143</v>
+      </c>
+      <c r="AC15" s="8">
+        <v>8.7042850000000005</v>
+      </c>
+      <c r="AD15" s="8">
+        <v>15.503052112676055</v>
+      </c>
+      <c r="AE15" s="6">
+        <v>0.90140845070422537</v>
+      </c>
       <c r="AF15" s="9"/>
-      <c r="AG15" s="5"/>
+      <c r="AG15" s="5">
+        <v>-444.80000000000001</v>
+      </c>
       <c r="AH15" s="10">
         <v>5</v>
       </c>
@@ -3798,7 +3942,9 @@
       <c r="AB20" s="8">
         <v>5.3781867647058821</v>
       </c>
-      <c r="AC20" s="8"/>
+      <c r="AC20" s="8">
+        <v>11.809558000000001</v>
+      </c>
       <c r="AD20" s="8">
         <v>18.742647058823529</v>
       </c>
@@ -4599,7 +4745,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>44</v>
@@ -4635,25 +4781,61 @@
       <c t="s" r="N27" s="4">
         <v>52</v>
       </c>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="6"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="6"/>
-      <c r="Z27" s="6"/>
-      <c r="AA27" s="8"/>
-      <c r="AB27" s="8"/>
-      <c r="AC27" s="8"/>
-      <c r="AD27" s="8"/>
-      <c r="AE27" s="6"/>
+      <c r="O27" s="5">
+        <v>2681.75</v>
+      </c>
+      <c r="P27" s="5">
+        <v>2681.75</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>-0.69310392181545599</v>
+      </c>
+      <c r="R27" s="7">
+        <v>33</v>
+      </c>
+      <c r="S27" s="6">
+        <v>-0.64516129032258063</v>
+      </c>
+      <c r="T27" s="6">
+        <v>0.17398952176750257</v>
+      </c>
+      <c r="U27" s="6">
+        <v>-0.15297980796121935</v>
+      </c>
+      <c r="V27" s="6">
+        <v>0.059803672974736648</v>
+      </c>
+      <c r="W27" s="6">
+        <v>0.040726577794350703</v>
+      </c>
+      <c r="X27" s="8">
+        <v>29.12435769230769</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="AA27" s="8">
+        <v>3.555051515151515</v>
+      </c>
+      <c r="AB27" s="8">
+        <v>9.3388875000000002</v>
+      </c>
+      <c r="AC27" s="8">
+        <v>13.358117999999999</v>
+      </c>
+      <c r="AD27" s="8">
+        <v>20.42371923076923</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>0.57692307692307687</v>
+      </c>
       <c r="AF27" s="9"/>
-      <c r="AG27" s="5"/>
+      <c r="AG27" s="5">
+        <v>0</v>
+      </c>
       <c r="AH27" s="10">
         <v>2</v>
       </c>
@@ -4694,7 +4876,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4730,25 +4912,61 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="O28" s="5">
+        <v>6722.8699999999999</v>
+      </c>
+      <c r="P28" s="5">
+        <v>6722.8699999999999</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>-0.050145596294888684</v>
+      </c>
+      <c r="R28" s="7">
+        <v>63</v>
+      </c>
+      <c r="S28" s="6">
+        <v>-0.18181818181818177</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0.00086239954067236161</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.32657067591668443</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.063605870707004589</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.056171545783274109</v>
+      </c>
+      <c r="X28" s="8">
+        <v>28.809374999999999</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>3.4491803278688526</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>9.4322906250000003</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>12.909374</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>19.850521874999998</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>0.625</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>375.10000000000002</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -4920,7 +5138,7 @@
         <v>19550</v>
       </c>
       <c r="B30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C30" s="4">
         <v>44</v>
@@ -4956,25 +5174,57 @@
       <c t="s" r="N30" s="4">
         <v>52</v>
       </c>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
+      <c r="O30" s="5">
+        <v>3264.1799999999998</v>
+      </c>
+      <c r="P30" s="5">
+        <v>3264.1799999999998</v>
+      </c>
       <c r="Q30" s="6"/>
-      <c r="R30" s="7"/>
+      <c r="R30" s="7">
+        <v>30</v>
+      </c>
       <c r="S30" s="6"/>
-      <c r="T30" s="6"/>
-      <c r="U30" s="6"/>
-      <c r="V30" s="6"/>
-      <c r="W30" s="6"/>
-      <c r="X30" s="8"/>
-      <c r="Y30" s="6"/>
-      <c r="Z30" s="6"/>
-      <c r="AA30" s="8"/>
-      <c r="AB30" s="8"/>
-      <c r="AC30" s="8"/>
-      <c r="AD30" s="8"/>
-      <c r="AE30" s="6"/>
+      <c r="T30" s="6">
+        <v>0.78115538971502796</v>
+      </c>
+      <c r="U30" s="6">
+        <v>0.39343473705494186</v>
+      </c>
+      <c r="V30" s="6">
+        <v>0.088037424406742282</v>
+      </c>
+      <c r="W30" s="6">
+        <v>0.038729481830046139</v>
+      </c>
+      <c r="X30" s="8">
+        <v>25.887176923076922</v>
+      </c>
+      <c r="Y30" s="6">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="Z30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="8">
+        <v>2.6161099999999999</v>
+      </c>
+      <c r="AB30" s="8">
+        <v>6.2756384615384615</v>
+      </c>
+      <c r="AC30" s="8">
+        <v>9.0166660000000007</v>
+      </c>
+      <c r="AD30" s="8">
+        <v>15.973076923076924</v>
+      </c>
+      <c r="AE30" s="6">
+        <v>0.84615384615384615</v>
+      </c>
       <c r="AF30" s="9"/>
-      <c r="AG30" s="5"/>
+      <c r="AG30" s="5">
+        <v>0</v>
+      </c>
       <c r="AH30" s="10">
         <v>3</v>
       </c>
@@ -5095,7 +5345,9 @@
       <c r="AB31" s="8">
         <v>2.6083333333333334</v>
       </c>
-      <c r="AC31" s="8"/>
+      <c r="AC31" s="8">
+        <v>5.9796870000000002</v>
+      </c>
       <c r="AD31" s="8">
         <v>13.69032258064516</v>
       </c>
@@ -5146,7 +5398,7 @@
         <v>19552</v>
       </c>
       <c r="B32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C32" s="4">
         <v>44</v>
@@ -5182,27 +5434,61 @@
       <c t="s" r="N32" s="4">
         <v>52</v>
       </c>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="7"/>
-      <c r="S32" s="6"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
-      <c r="V32" s="6"/>
-      <c r="W32" s="6"/>
-      <c r="X32" s="8"/>
-      <c r="Y32" s="6"/>
-      <c r="Z32" s="6"/>
-      <c r="AA32" s="8"/>
-      <c r="AB32" s="8"/>
+      <c r="O32" s="5">
+        <v>10130.959999999999</v>
+      </c>
+      <c r="P32" s="5">
+        <v>10130.959999999999</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>-0.30874103853693524</v>
+      </c>
+      <c r="R32" s="7">
+        <v>92</v>
+      </c>
+      <c r="S32" s="6">
+        <v>-0.32846715328467158</v>
+      </c>
+      <c r="T32" s="6">
+        <v>0.26137874396898225</v>
+      </c>
+      <c r="U32" s="6">
+        <v>-0.079162527539344746</v>
+      </c>
+      <c r="V32" s="6">
+        <v>0.028323771883414804</v>
+      </c>
+      <c r="W32" s="6">
+        <v>0.013199834961346212</v>
+      </c>
+      <c r="X32" s="8">
+        <v>24.656923076923078</v>
+      </c>
+      <c r="Y32" s="6">
+        <v>0.93846153846153846</v>
+      </c>
+      <c r="Z32" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="8">
+        <v>2.9344206521739129</v>
+      </c>
+      <c r="AB32" s="8">
+        <v>6.5825515625</v>
+      </c>
       <c r="AC32" s="8">
         <v>9.7239579999999997</v>
       </c>
-      <c r="AD32" s="8"/>
-      <c r="AE32" s="6"/>
+      <c r="AD32" s="8">
+        <v>15.467180000000001</v>
+      </c>
+      <c r="AE32" s="6">
+        <v>0.83076923076923082</v>
+      </c>
       <c r="AF32" s="9"/>
-      <c r="AG32" s="5"/>
+      <c r="AG32" s="5">
+        <v>0</v>
+      </c>
       <c r="AH32" s="10">
         <v>4</v>
       </c>
@@ -5243,7 +5529,7 @@
         <v>19553</v>
       </c>
       <c r="B33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C33" s="4">
         <v>44</v>
@@ -5277,25 +5563,61 @@
       <c t="s" r="N33" s="4">
         <v>52</v>
       </c>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6"/>
-      <c r="X33" s="8"/>
-      <c r="Y33" s="6"/>
-      <c r="Z33" s="6"/>
-      <c r="AA33" s="8"/>
-      <c r="AB33" s="8"/>
-      <c r="AC33" s="8"/>
-      <c r="AD33" s="8"/>
-      <c r="AE33" s="6"/>
+      <c r="O33" s="5">
+        <v>5972.04</v>
+      </c>
+      <c r="P33" s="5">
+        <v>5972.04</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>-0.42148941261032258</v>
+      </c>
+      <c r="R33" s="7">
+        <v>46</v>
+      </c>
+      <c r="S33" s="6">
+        <v>-0.54000000000000004</v>
+      </c>
+      <c r="T33" s="6">
+        <v>0.37921686726813619</v>
+      </c>
+      <c r="U33" s="6">
+        <v>-0.0028703257178451583</v>
+      </c>
+      <c r="V33" s="6">
+        <v>0.014934092872787188</v>
+      </c>
+      <c r="W33" s="6">
+        <v>-0.01686576111345537</v>
+      </c>
+      <c r="X33" s="8">
+        <v>24.046664999999997</v>
+      </c>
+      <c r="Y33" s="6">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="Z33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="8">
+        <v>1.9612326086956522</v>
+      </c>
+      <c r="AB33" s="8">
+        <v>6.4950000000000001</v>
+      </c>
+      <c r="AC33" s="8">
+        <v>8.4416659999999997</v>
+      </c>
+      <c r="AD33" s="8">
+        <v>15.395</v>
+      </c>
+      <c r="AE33" s="6">
+        <v>1</v>
+      </c>
       <c r="AF33" s="9"/>
-      <c r="AG33" s="5"/>
+      <c r="AG33" s="5">
+        <v>0</v>
+      </c>
       <c r="AH33" s="10">
         <v>5</v>
       </c>
@@ -5336,7 +5658,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>44</v>
@@ -5372,25 +5694,61 @@
       <c t="s" r="N34" s="4">
         <v>52</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="6"/>
+      <c r="O34" s="5">
+        <v>9233.4300000000003</v>
+      </c>
+      <c r="P34" s="5">
+        <v>9233.4300000000003</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>0.27950462903299567</v>
+      </c>
+      <c r="R34" s="7">
+        <v>103</v>
+      </c>
+      <c r="S34" s="6">
+        <v>0.51470588235294112</v>
+      </c>
+      <c r="T34" s="6">
+        <v>3.9349933448350178</v>
+      </c>
+      <c r="U34" s="6">
+        <v>3.6047076330247805</v>
+      </c>
+      <c r="V34" s="6">
+        <v>0.086384799581520635</v>
+      </c>
+      <c r="W34" s="6">
+        <v>0.057447557408243741</v>
+      </c>
+      <c r="X34" s="8">
+        <v>20.617982894736841</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>0.026315789473684209</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>7.8630715686274515</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>1.6407402777777778</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>10.276923999999999</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>15.946930263157894</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0.89473684210526316</v>
+      </c>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5">
+        <v>0</v>
+      </c>
       <c r="AH34" s="10">
         <v>4</v>
       </c>
@@ -5661,7 +6019,7 @@
         <v>19563</v>
       </c>
       <c r="B37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C37" s="4">
         <v>44</v>
@@ -5697,27 +6055,61 @@
       <c t="s" r="N37" s="4">
         <v>52</v>
       </c>
-      <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="7"/>
-      <c r="S37" s="6"/>
-      <c r="T37" s="6"/>
-      <c r="U37" s="6"/>
-      <c r="V37" s="6"/>
-      <c r="W37" s="6"/>
-      <c r="X37" s="8"/>
-      <c r="Y37" s="6"/>
-      <c r="Z37" s="6"/>
-      <c r="AA37" s="8"/>
-      <c r="AB37" s="8"/>
+      <c r="O37" s="5">
+        <v>4753.3500000000004</v>
+      </c>
+      <c r="P37" s="5">
+        <v>4753.3500000000004</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>-0.16701131014758919</v>
+      </c>
+      <c r="R37" s="7">
+        <v>53</v>
+      </c>
+      <c r="S37" s="6">
+        <v>-0.23188405797101452</v>
+      </c>
+      <c r="T37" s="6">
+        <v>-0.74276539703577471</v>
+      </c>
+      <c r="U37" s="6">
+        <v>-1.0750110763987504</v>
+      </c>
+      <c r="V37" s="6">
+        <v>0.021296664457698254</v>
+      </c>
+      <c r="W37" s="6">
+        <v>0.0061389335942019828</v>
+      </c>
+      <c r="X37" s="8">
+        <v>27.844046428571428</v>
+      </c>
+      <c r="Y37" s="6">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="Z37" s="6">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="AA37" s="8">
+        <v>3.6854944444444442</v>
+      </c>
+      <c r="AB37" s="8">
+        <v>11.376923076923077</v>
+      </c>
       <c r="AC37" s="8">
         <v>14.953113</v>
       </c>
-      <c r="AD37" s="8"/>
-      <c r="AE37" s="6"/>
+      <c r="AD37" s="8">
+        <v>20.783928571428572</v>
+      </c>
+      <c r="AE37" s="6">
+        <v>0.75</v>
+      </c>
       <c r="AF37" s="9"/>
-      <c r="AG37" s="5"/>
+      <c r="AG37" s="5">
+        <v>0</v>
+      </c>
       <c r="AH37" s="10">
         <v>2</v>
       </c>
@@ -5889,7 +6281,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -5925,25 +6317,61 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="O39" s="5">
+        <v>4321</v>
+      </c>
+      <c r="P39" s="5">
+        <v>4321</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>0.10013493902283788</v>
+      </c>
+      <c r="R39" s="7">
+        <v>45</v>
+      </c>
+      <c r="S39" s="6">
+        <v>-0.081632653061224469</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.32557218236519325</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.030856884980328632</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.10715227956491553</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.060005785697755158</v>
+      </c>
+      <c r="X39" s="8">
+        <v>17.733334615384617</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>1.9855555555555555</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>4.3999999999999995</v>
+      </c>
+      <c r="AC39" s="8">
+        <v>6.5993579999999996</v>
+      </c>
+      <c r="AD39" s="8">
+        <v>11.594230769230769</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.92307692307692313</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6246,7 +6674,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6282,25 +6710,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>4911.6300000000001</v>
+      </c>
+      <c r="P42" s="5">
+        <v>4911.6300000000001</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.30270958619397259</v>
+      </c>
+      <c r="R42" s="7">
+        <v>48</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.30434782608695654</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.34369962721133307</v>
+      </c>
+      <c r="U42" s="6">
+        <v>-0.034681887682907711</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.062673593084169615</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.017869729600967499</v>
+      </c>
+      <c r="X42" s="8">
+        <v>29.477619999999998</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.74285714285714288</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>6.0235500000000002</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>8.9328571428571415</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>14.899523</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>21.842379999999999</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -6734,7 +7198,7 @@
         <v>19596</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>44</v>
@@ -6768,25 +7232,59 @@
       <c t="s" r="N46" s="4">
         <v>52</v>
       </c>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
+      <c r="O46" s="5">
+        <v>7533.7600000000002</v>
+      </c>
+      <c r="P46" s="5">
+        <v>7533.7600000000002</v>
+      </c>
       <c r="Q46" s="6"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
-      <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="8"/>
-      <c r="Y46" s="6"/>
-      <c r="Z46" s="6"/>
-      <c r="AA46" s="8"/>
-      <c r="AB46" s="8"/>
-      <c r="AC46" s="8"/>
-      <c r="AD46" s="8"/>
-      <c r="AE46" s="6"/>
+      <c r="R46" s="7">
+        <v>65</v>
+      </c>
+      <c r="S46" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="T46" s="6">
+        <v>0.35364289544662952</v>
+      </c>
+      <c r="U46" s="6">
+        <v>-0.06616474376672471</v>
+      </c>
+      <c r="V46" s="6">
+        <v>0.0063635555154398331</v>
+      </c>
+      <c r="W46" s="6">
+        <v>-0.04790151265769018</v>
+      </c>
+      <c r="X46" s="8">
+        <v>40.144948484848484</v>
+      </c>
+      <c r="Y46" s="6">
+        <v>0.93939393939393945</v>
+      </c>
+      <c r="Z46" s="6">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="AA46" s="8">
+        <v>7.660512307692307</v>
+      </c>
+      <c r="AB46" s="8">
+        <v>15.555912903225806</v>
+      </c>
+      <c r="AC46" s="8">
+        <v>25.357382999999999</v>
+      </c>
+      <c r="AD46" s="8">
+        <v>31.326263636363635</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>0.30303030303030304</v>
+      </c>
       <c r="AF46" s="9"/>
-      <c r="AG46" s="5"/>
+      <c r="AG46" s="5">
+        <v>48.899999999999999</v>
+      </c>
       <c r="AH46" s="10">
         <v>3</v>
       </c>
@@ -7216,7 +7714,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>44</v>
@@ -7252,25 +7750,61 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
-      <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="6"/>
+      <c r="O50" s="5">
+        <v>4772.2200000000003</v>
+      </c>
+      <c r="P50" s="5">
+        <v>4772.2200000000003</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>-0.25317370892018776</v>
+      </c>
+      <c r="R50" s="7">
+        <v>60</v>
+      </c>
+      <c r="S50" s="6">
+        <v>-0.25</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0.24103186776804086</v>
+      </c>
+      <c r="U50" s="6">
+        <v>-0.071713563079656845</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0.083118548600022629</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.034237734220132342</v>
+      </c>
+      <c r="X50" s="8">
+        <v>25.67807105263158</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AA50" s="8">
+        <v>2.7612127272727274</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>7.0964921052631578</v>
+      </c>
+      <c r="AC50" s="8">
+        <v>9.8771920000000009</v>
+      </c>
+      <c r="AD50" s="8">
+        <v>17.832018421052634</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>0.71052631578947367</v>
+      </c>
       <c r="AF50" s="9"/>
-      <c r="AG50" s="5"/>
+      <c r="AG50" s="5">
+        <v>-66.900000000000006</v>
+      </c>
       <c r="AH50" s="10">
         <v>4</v>
       </c>
@@ -7406,7 +7940,7 @@
         <v>19606</v>
       </c>
       <c r="B52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C52" s="4">
         <v>44</v>
@@ -7442,25 +7976,61 @@
       <c t="s" r="N52" s="4">
         <v>52</v>
       </c>
-      <c r="O52" s="5"/>
-      <c r="P52" s="5"/>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="7"/>
-      <c r="S52" s="6"/>
-      <c r="T52" s="6"/>
-      <c r="U52" s="6"/>
-      <c r="V52" s="6"/>
-      <c r="W52" s="6"/>
-      <c r="X52" s="8"/>
-      <c r="Y52" s="6"/>
-      <c r="Z52" s="6"/>
-      <c r="AA52" s="8"/>
-      <c r="AB52" s="8"/>
-      <c r="AC52" s="8"/>
-      <c r="AD52" s="8"/>
-      <c r="AE52" s="6"/>
+      <c r="O52" s="5">
+        <v>3665.3000000000002</v>
+      </c>
+      <c r="P52" s="5">
+        <v>3665.3000000000002</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>-0.47559911295514701</v>
+      </c>
+      <c r="R52" s="7">
+        <v>41</v>
+      </c>
+      <c r="S52" s="6">
+        <v>-0.44594594594594594</v>
+      </c>
+      <c r="T52" s="6">
+        <v>-0.20669522276484872</v>
+      </c>
+      <c r="U52" s="6">
+        <v>-0.54609445338717155</v>
+      </c>
+      <c r="V52" s="6">
+        <v>0.052471557580552754</v>
+      </c>
+      <c r="W52" s="6">
+        <v>0.023660819032548495</v>
+      </c>
+      <c r="X52" s="8">
+        <v>26.836276470588235</v>
+      </c>
+      <c r="Y52" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="8">
+        <v>5.6531000000000002</v>
+      </c>
+      <c r="AB52" s="8">
+        <v>2.693135294117647</v>
+      </c>
+      <c r="AC52" s="8">
+        <v>8.417211</v>
+      </c>
+      <c r="AD52" s="8">
+        <v>16.288235294117644</v>
+      </c>
+      <c r="AE52" s="6">
+        <v>0.70588235294117652</v>
+      </c>
       <c r="AF52" s="9"/>
-      <c r="AG52" s="5"/>
+      <c r="AG52" s="5">
+        <v>-1241.5</v>
+      </c>
       <c r="AH52" s="10">
         <v>1</v>
       </c>
@@ -7577,7 +8147,9 @@
       <c r="AB53" s="8">
         <v>2.7480000000000002</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="8">
+        <v>5.2140000000000004</v>
+      </c>
       <c r="AD53" s="8">
         <v>12.16</v>
       </c>
@@ -7759,7 +8331,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -7795,25 +8367,61 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
-      <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="O55" s="5">
+        <v>5339</v>
+      </c>
+      <c r="P55" s="5">
+        <v>5339</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>0.012458991523334406</v>
+      </c>
+      <c r="R55" s="7">
+        <v>56</v>
+      </c>
+      <c r="S55" s="6">
+        <v>-0.05084745762711862</v>
+      </c>
+      <c r="T55" s="6">
+        <v>-0.00062371230567522006</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.32697696197789849</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.094048604607604419</v>
+      </c>
+      <c r="W55" s="6">
+        <v>0.046695167634388461</v>
+      </c>
+      <c r="X55" s="8">
+        <v>32.150417499999996</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.21951219512195122</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>2.8415145454545452</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>10.4475</v>
+      </c>
+      <c r="AC55" s="8">
+        <v>13.3675</v>
+      </c>
+      <c r="AD55" s="8">
+        <v>20.304167499999998</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0.375</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -8114,7 +8722,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8150,25 +8758,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="O58" s="5">
+        <v>4712.8699999999999</v>
+      </c>
+      <c r="P58" s="5">
+        <v>4712.8699999999999</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>-0.01066612366909625</v>
+      </c>
+      <c r="R58" s="7">
+        <v>56</v>
+      </c>
+      <c r="S58" s="6">
+        <v>0.056603773584905648</v>
+      </c>
+      <c r="T58" s="6">
+        <v>7.1478110578055407</v>
+      </c>
+      <c r="U58" s="6">
+        <v>6.7981578740767299</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.011583387617311744</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.0068024367317579305</v>
+      </c>
+      <c r="X58" s="8">
+        <v>23.628173809523808</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>2.9772727272727271</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>7.1535714285714285</v>
+      </c>
+      <c r="AC58" s="8">
+        <v>10.373338</v>
+      </c>
+      <c r="AD58" s="8">
+        <v>17.361904761904764</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.73809523809523814</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-59.700000000000003</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -8598,7 +9242,7 @@
         <v>19625</v>
       </c>
       <c r="B62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C62" s="4">
         <v>44</v>
@@ -8634,25 +9278,61 @@
       <c t="s" r="N62" s="4">
         <v>52</v>
       </c>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="7"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
-      <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
-      <c r="X62" s="8"/>
-      <c r="Y62" s="6"/>
-      <c r="Z62" s="6"/>
-      <c r="AA62" s="8"/>
-      <c r="AB62" s="8"/>
-      <c r="AC62" s="8"/>
-      <c r="AD62" s="8"/>
-      <c r="AE62" s="6"/>
+      <c r="O62" s="5">
+        <v>5649.6300000000001</v>
+      </c>
+      <c r="P62" s="5">
+        <v>5649.6300000000001</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>-0.033297799710141351</v>
+      </c>
+      <c r="R62" s="7">
+        <v>53</v>
+      </c>
+      <c r="S62" s="6">
+        <v>-0.20895522388059706</v>
+      </c>
+      <c r="T62" s="6">
+        <v>-0.0003591916638788735</v>
+      </c>
+      <c r="U62" s="6">
+        <v>-0.29795213137851506</v>
+      </c>
+      <c r="V62" s="6">
+        <v>0.013276002145273229</v>
+      </c>
+      <c r="W62" s="6">
+        <v>-0.0028312473560215446</v>
+      </c>
+      <c r="X62" s="8">
+        <v>22.952223333333333</v>
+      </c>
+      <c r="Y62" s="6">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="Z62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="8">
+        <v>2.8962264150943398</v>
+      </c>
+      <c r="AB62" s="8">
+        <v>4.2516666666666669</v>
+      </c>
+      <c r="AC62" s="8">
+        <v>7.3716660000000003</v>
+      </c>
+      <c r="AD62" s="8">
+        <v>14.317776666666667</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF62" s="9"/>
-      <c r="AG62" s="5"/>
+      <c r="AG62" s="5">
+        <v>-290.30000000000001</v>
+      </c>
       <c r="AH62" s="10">
         <v>4</v>
       </c>
@@ -9124,7 +9804,9 @@
       <c r="AB66" s="8">
         <v>8.1446428571428573</v>
       </c>
-      <c r="AC66" s="8"/>
+      <c r="AC66" s="8">
+        <v>13.361307999999999</v>
+      </c>
       <c r="AD66" s="8">
         <v>18.538170967741937</v>
       </c>
@@ -9695,7 +10377,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>44</v>
@@ -9729,25 +10411,61 @@
       <c t="s" r="N71" s="4">
         <v>52</v>
       </c>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="6"/>
-      <c r="Z71" s="6"/>
-      <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
-      <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="6"/>
+      <c r="O71" s="5">
+        <v>4609.3500000000004</v>
+      </c>
+      <c r="P71" s="5">
+        <v>4609.3500000000004</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>-0.0086481301456482473</v>
+      </c>
+      <c r="R71" s="7">
+        <v>55</v>
+      </c>
+      <c r="S71" s="6">
+        <v>-0.098360655737704916</v>
+      </c>
+      <c r="T71" s="6">
+        <v>0.26830455487216198</v>
+      </c>
+      <c r="U71" s="6">
+        <v>-0.048262857018885517</v>
+      </c>
+      <c r="V71" s="6">
+        <v>0.068002538318851891</v>
+      </c>
+      <c r="W71" s="6">
+        <v>0.011634503780359485</v>
+      </c>
+      <c r="X71" s="8">
+        <v>21.690835</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="8">
+        <v>2.8643784313725491</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>4.211665</v>
+      </c>
+      <c r="AC71" s="8">
+        <v>7.0308320000000002</v>
+      </c>
+      <c r="AD71" s="8">
+        <v>14.98</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>0.90000000000000002</v>
+      </c>
       <c r="AF71" s="9"/>
-      <c r="AG71" s="5"/>
+      <c r="AG71" s="5">
+        <v>-99</v>
+      </c>
       <c r="AH71" s="10">
         <v>4</v>
       </c>
@@ -10137,7 +10855,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10173,25 +10891,61 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="O75" s="5">
+        <v>3890.3200000000002</v>
+      </c>
+      <c r="P75" s="5">
+        <v>3890.3200000000002</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>-0.050516193590901315</v>
+      </c>
+      <c r="R75" s="7">
+        <v>43</v>
+      </c>
+      <c r="S75" s="6">
+        <v>-0.065217391304347783</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.32204548726068805</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.053620010693207751</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.024786906989656379</v>
+      </c>
+      <c r="X75" s="8">
+        <v>26.984720833333331</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>5.3511363636363631</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>9.0905782608695649</v>
+      </c>
+      <c r="AC75" s="8">
+        <v>15.250579</v>
+      </c>
+      <c r="AD75" s="8">
+        <v>21.650000000000002</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-195.80000000000001</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10232,7 +10986,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10266,25 +11020,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>6346.4200000000001</v>
+      </c>
+      <c r="P76" s="5">
+        <v>6346.4200000000001</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.074326137689614935</v>
+      </c>
+      <c r="R76" s="7">
+        <v>78</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.21999999999999997</v>
+      </c>
+      <c r="T76" s="6">
+        <v>-1.153722035415242</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-1.5356696531272749</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.024413448842024319</v>
+      </c>
+      <c r="W76" s="6">
+        <v>-0.0077085979181964002</v>
+      </c>
+      <c r="X76" s="8">
+        <v>25</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.57777777777777772</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.044444444444444446</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>2.6567103896103896</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>5.5174804878048782</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>8.3312469999999994</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>16.635555555555555</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.71111111111111114</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>0</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -10454,7 +11244,7 @@
         <v>19666</v>
       </c>
       <c r="B78" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C78" s="4">
         <v>44</v>
@@ -10488,25 +11278,61 @@
       <c t="s" r="N78" s="4">
         <v>52</v>
       </c>
-      <c r="O78" s="5"/>
-      <c r="P78" s="5"/>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="7"/>
-      <c r="S78" s="6"/>
-      <c r="T78" s="6"/>
-      <c r="U78" s="6"/>
-      <c r="V78" s="6"/>
-      <c r="W78" s="6"/>
-      <c r="X78" s="8"/>
-      <c r="Y78" s="6"/>
-      <c r="Z78" s="6"/>
-      <c r="AA78" s="8"/>
-      <c r="AB78" s="8"/>
-      <c r="AC78" s="8"/>
-      <c r="AD78" s="8"/>
-      <c r="AE78" s="6"/>
+      <c r="O78" s="5">
+        <v>6288.3900000000003</v>
+      </c>
+      <c r="P78" s="5">
+        <v>6288.3900000000003</v>
+      </c>
+      <c r="Q78" s="6">
+        <v>-0.064213753180850763</v>
+      </c>
+      <c r="R78" s="7">
+        <v>57</v>
+      </c>
+      <c r="S78" s="6">
+        <v>-0.16176470588235292</v>
+      </c>
+      <c r="T78" s="6">
+        <v>0.051833410459592992</v>
+      </c>
+      <c r="U78" s="6">
+        <v>-0.26310411727008021</v>
+      </c>
+      <c r="V78" s="6">
+        <v>0.018094536121328351</v>
+      </c>
+      <c r="W78" s="6">
+        <v>-0.0031907213134045437</v>
+      </c>
+      <c r="X78" s="8">
+        <v>22.755555555555556</v>
+      </c>
+      <c r="Y78" s="6">
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="Z78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="8">
+        <v>3.1035714285714286</v>
+      </c>
+      <c r="AB78" s="8">
+        <v>4.0818511111111109</v>
+      </c>
+      <c r="AC78" s="8">
+        <v>7.2455540000000003</v>
+      </c>
+      <c r="AD78" s="8">
+        <v>15.213704444444446</v>
+      </c>
+      <c r="AE78" s="6">
+        <v>0.97777777777777775</v>
+      </c>
       <c r="AF78" s="9"/>
-      <c r="AG78" s="5"/>
+      <c r="AG78" s="5">
+        <v>0</v>
+      </c>
       <c r="AH78" s="10">
         <v>5</v>
       </c>
@@ -11164,7 +11990,7 @@
         <v>19685</v>
       </c>
       <c r="B84" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C84" s="4">
         <v>44</v>
@@ -11200,25 +12026,61 @@
       <c t="s" r="N84" s="4">
         <v>52</v>
       </c>
-      <c r="O84" s="5"/>
-      <c r="P84" s="5"/>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="7"/>
-      <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
-      <c r="V84" s="6"/>
-      <c r="W84" s="6"/>
-      <c r="X84" s="8"/>
-      <c r="Y84" s="6"/>
-      <c r="Z84" s="6"/>
-      <c r="AA84" s="8"/>
-      <c r="AB84" s="8"/>
-      <c r="AC84" s="8"/>
-      <c r="AD84" s="8"/>
-      <c r="AE84" s="6"/>
+      <c r="O84" s="5">
+        <v>3757.9000000000001</v>
+      </c>
+      <c r="P84" s="5">
+        <v>3757.9000000000001</v>
+      </c>
+      <c r="Q84" s="6">
+        <v>-0.090405189524132124</v>
+      </c>
+      <c r="R84" s="7">
+        <v>42</v>
+      </c>
+      <c r="S84" s="6">
+        <v>0.050000000000000044</v>
+      </c>
+      <c r="T84" s="6">
+        <v>0</v>
+      </c>
+      <c r="U84" s="6">
+        <v>-0.3693924798424652</v>
+      </c>
+      <c r="V84" s="6">
+        <v>0.0693063945288592</v>
+      </c>
+      <c r="W84" s="6">
+        <v>0.019794699167087999</v>
+      </c>
+      <c r="X84" s="8">
+        <v>46.054322222222218</v>
+      </c>
+      <c r="Y84" s="6">
+        <v>0.40740740740740738</v>
+      </c>
+      <c r="Z84" s="6">
+        <v>0.37037037037037035</v>
+      </c>
+      <c r="AA84" s="8">
+        <v>5.9753795454545449</v>
+      </c>
+      <c r="AB84" s="8">
+        <v>23.399332000000001</v>
+      </c>
+      <c r="AC84" s="8">
+        <v>29.055505</v>
+      </c>
+      <c r="AD84" s="8">
+        <v>33.970370370370375</v>
+      </c>
+      <c r="AE84" s="6">
+        <v>0.22222222222222221</v>
+      </c>
       <c r="AF84" s="9"/>
-      <c r="AG84" s="5"/>
+      <c r="AG84" s="5">
+        <v>0</v>
+      </c>
       <c r="AH84" s="10">
         <v>2</v>
       </c>
@@ -11390,7 +12252,7 @@
         <v>19688</v>
       </c>
       <c r="B86" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C86" s="4">
         <v>44</v>
@@ -11426,27 +12288,61 @@
       <c t="s" r="N86" s="4">
         <v>52</v>
       </c>
-      <c r="O86" s="5"/>
-      <c r="P86" s="5"/>
-      <c r="Q86" s="6"/>
-      <c r="R86" s="7"/>
-      <c r="S86" s="6"/>
-      <c r="T86" s="6"/>
-      <c r="U86" s="6"/>
-      <c r="V86" s="6"/>
-      <c r="W86" s="6"/>
-      <c r="X86" s="8"/>
-      <c r="Y86" s="6"/>
-      <c r="Z86" s="6"/>
-      <c r="AA86" s="8"/>
-      <c r="AB86" s="8"/>
+      <c r="O86" s="5">
+        <v>3945.3000000000002</v>
+      </c>
+      <c r="P86" s="5">
+        <v>3945.3000000000002</v>
+      </c>
+      <c r="Q86" s="6">
+        <v>-0.2298592770011888</v>
+      </c>
+      <c r="R86" s="7">
+        <v>45</v>
+      </c>
+      <c r="S86" s="6">
+        <v>-0.16666666666666663</v>
+      </c>
+      <c r="T86" s="6">
+        <v>0.38288910855955183</v>
+      </c>
+      <c r="U86" s="6">
+        <v>0.02474650850378932</v>
+      </c>
+      <c r="V86" s="6">
+        <v>0.032565457633133094</v>
+      </c>
+      <c r="W86" s="6">
+        <v>0.0032495627708919472</v>
+      </c>
+      <c r="X86" s="8">
+        <v>29.308334615384616</v>
+      </c>
+      <c r="Y86" s="6">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Z86" s="6">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AA86" s="8">
+        <v>9.901851111111112</v>
+      </c>
+      <c r="AB86" s="8">
+        <v>3.7680541666666669</v>
+      </c>
       <c r="AC86" s="8">
-        <v>13.061119</v>
-      </c>
-      <c r="AD86" s="8"/>
-      <c r="AE86" s="6"/>
+        <v>13.329166000000001</v>
+      </c>
+      <c r="AD86" s="8">
+        <v>21.110896153846152</v>
+      </c>
+      <c r="AE86" s="6">
+        <v>0.57692307692307687</v>
+      </c>
       <c r="AF86" s="9"/>
-      <c r="AG86" s="5"/>
+      <c r="AG86" s="5">
+        <v>0</v>
+      </c>
       <c r="AH86" s="10">
         <v>3</v>
       </c>
@@ -11840,7 +12736,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>44</v>
@@ -11876,25 +12772,61 @@
       <c t="s" r="N90" s="4">
         <v>52</v>
       </c>
-      <c r="O90" s="5"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="7"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
-      <c r="V90" s="6"/>
-      <c r="W90" s="6"/>
-      <c r="X90" s="8"/>
-      <c r="Y90" s="6"/>
-      <c r="Z90" s="6"/>
-      <c r="AA90" s="8"/>
-      <c r="AB90" s="8"/>
-      <c r="AC90" s="8"/>
-      <c r="AD90" s="8"/>
-      <c r="AE90" s="6"/>
+      <c r="O90" s="5">
+        <v>4352.5200000000004</v>
+      </c>
+      <c r="P90" s="5">
+        <v>4352.5200000000004</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>0.18196951469545941</v>
+      </c>
+      <c r="R90" s="7">
+        <v>48</v>
+      </c>
+      <c r="S90" s="6">
+        <v>0.021276595744680771</v>
+      </c>
+      <c r="T90" s="6">
+        <v>0</v>
+      </c>
+      <c r="U90" s="6">
+        <v>-6.0074439634970078</v>
+      </c>
+      <c r="V90" s="6">
+        <v>0.15656665563857258</v>
+      </c>
+      <c r="W90" s="6">
+        <v>0.11251631238914467</v>
+      </c>
+      <c r="X90" s="8">
+        <v>26.800000000000001</v>
+      </c>
+      <c r="Y90" s="6">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="Z90" s="6">
+        <v>0.13793103448275862</v>
+      </c>
+      <c r="AA90" s="8">
+        <v>7.893972340425532</v>
+      </c>
+      <c r="AB90" s="8">
+        <v>7.4934535714285717</v>
+      </c>
+      <c r="AC90" s="8">
+        <v>16.386904000000001</v>
+      </c>
+      <c r="AD90" s="8">
+        <v>22.480458620689657</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>0.62068965517241381</v>
+      </c>
       <c r="AF90" s="9"/>
-      <c r="AG90" s="5"/>
+      <c r="AG90" s="5">
+        <v>-441.62</v>
+      </c>
       <c r="AH90" s="10">
         <v>2</v>
       </c>
@@ -12402,7 +13334,9 @@
       <c r="AB94" s="8">
         <v>4.4011928571428571</v>
       </c>
-      <c r="AC94" s="8"/>
+      <c r="AC94" s="8">
+        <v>9.939152</v>
+      </c>
       <c r="AD94" s="8">
         <v>16.198150000000002</v>
       </c>
@@ -13816,7 +14750,7 @@
         <v>19725</v>
       </c>
       <c r="B106" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C106" s="4">
         <v>44</v>
@@ -13852,25 +14786,61 @@
       <c t="s" r="N106" s="4">
         <v>52</v>
       </c>
-      <c r="O106" s="5"/>
-      <c r="P106" s="5"/>
-      <c r="Q106" s="6"/>
-      <c r="R106" s="7"/>
-      <c r="S106" s="6"/>
-      <c r="T106" s="6"/>
-      <c r="U106" s="6"/>
-      <c r="V106" s="6"/>
-      <c r="W106" s="6"/>
-      <c r="X106" s="8"/>
-      <c r="Y106" s="6"/>
-      <c r="Z106" s="6"/>
-      <c r="AA106" s="8"/>
-      <c r="AB106" s="8"/>
-      <c r="AC106" s="8"/>
-      <c r="AD106" s="8"/>
-      <c r="AE106" s="6"/>
+      <c r="O106" s="5">
+        <v>2791.9899999999998</v>
+      </c>
+      <c r="P106" s="5">
+        <v>2791.9899999999998</v>
+      </c>
+      <c r="Q106" s="6">
+        <v>0.59296513949905849</v>
+      </c>
+      <c r="R106" s="7">
+        <v>38</v>
+      </c>
+      <c r="S106" s="6">
+        <v>0.65217391304347827</v>
+      </c>
+      <c r="T106" s="6">
+        <v>0.40060211533708939</v>
+      </c>
+      <c r="U106" s="6">
+        <v>0.061378120981808677</v>
+      </c>
+      <c r="V106" s="6">
+        <v>0.020552007707763997</v>
+      </c>
+      <c r="W106" s="6">
+        <v>-0.027933122969638149</v>
+      </c>
+      <c r="X106" s="8">
+        <v>18.948486363636363</v>
+      </c>
+      <c r="Y106" s="6">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="Z106" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA106" s="8">
+        <v>3.2723684210526316</v>
+      </c>
+      <c r="AB106" s="8">
+        <v>1.6606045454545453</v>
+      </c>
+      <c r="AC106" s="8">
+        <v>4.4545450000000004</v>
+      </c>
+      <c r="AD106" s="8">
+        <v>11.427272727272728</v>
+      </c>
+      <c r="AE106" s="6">
+        <v>1</v>
+      </c>
       <c r="AF106" s="9"/>
-      <c r="AG106" s="5"/>
+      <c r="AG106" s="5">
+        <v>0</v>
+      </c>
       <c r="AH106" s="10">
         <v>4</v>
       </c>
@@ -13911,7 +14881,7 @@
         <v>19727</v>
       </c>
       <c r="B107" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C107" s="4">
         <v>44</v>
@@ -13947,25 +14917,61 @@
       <c t="s" r="N107" s="4">
         <v>52</v>
       </c>
-      <c r="O107" s="5"/>
-      <c r="P107" s="5"/>
-      <c r="Q107" s="6"/>
-      <c r="R107" s="7"/>
-      <c r="S107" s="6"/>
-      <c r="T107" s="6"/>
-      <c r="U107" s="6"/>
-      <c r="V107" s="6"/>
-      <c r="W107" s="6"/>
-      <c r="X107" s="8"/>
-      <c r="Y107" s="6"/>
-      <c r="Z107" s="6"/>
-      <c r="AA107" s="8"/>
-      <c r="AB107" s="8"/>
-      <c r="AC107" s="8"/>
-      <c r="AD107" s="8"/>
-      <c r="AE107" s="6"/>
+      <c r="O107" s="5">
+        <v>2696.1399999999999</v>
+      </c>
+      <c r="P107" s="5">
+        <v>2696.1399999999999</v>
+      </c>
+      <c r="Q107" s="6">
+        <v>-0.45188597543373166</v>
+      </c>
+      <c r="R107" s="7">
+        <v>32</v>
+      </c>
+      <c r="S107" s="6">
+        <v>-0.31914893617021278</v>
+      </c>
+      <c r="T107" s="6">
+        <v>-21.544386715823364</v>
+      </c>
+      <c r="U107" s="6">
+        <v>-21.866569540157411</v>
+      </c>
+      <c r="V107" s="6">
+        <v>0.031234097635879445</v>
+      </c>
+      <c r="W107" s="6">
+        <v>-0.012661990846172677</v>
+      </c>
+      <c r="X107" s="8">
+        <v>28.500982352941179</v>
+      </c>
+      <c r="Y107" s="6">
+        <v>0.88235294117647056</v>
+      </c>
+      <c r="Z107" s="6">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AA107" s="8">
+        <v>7.9927766666666669</v>
+      </c>
+      <c r="AB107" s="8">
+        <v>4.3284294117647057</v>
+      </c>
+      <c r="AC107" s="8">
+        <v>13.549018999999999</v>
+      </c>
+      <c r="AD107" s="8">
+        <v>20.5</v>
+      </c>
+      <c r="AE107" s="6">
+        <v>0.82352941176470584</v>
+      </c>
       <c r="AF107" s="9"/>
-      <c r="AG107" s="5"/>
+      <c r="AG107" s="5">
+        <v>-76.900000000000006</v>
+      </c>
       <c r="AH107" s="10">
         <v>2</v>
       </c>
@@ -14099,7 +15105,7 @@
         <v>19730</v>
       </c>
       <c r="B109" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C109" s="4">
         <v>44</v>
@@ -14133,25 +15139,61 @@
       <c t="s" r="N109" s="4">
         <v>52</v>
       </c>
-      <c r="O109" s="5"/>
-      <c r="P109" s="5"/>
-      <c r="Q109" s="6"/>
-      <c r="R109" s="7"/>
-      <c r="S109" s="6"/>
-      <c r="T109" s="6"/>
-      <c r="U109" s="6"/>
-      <c r="V109" s="6"/>
-      <c r="W109" s="6"/>
-      <c r="X109" s="8"/>
-      <c r="Y109" s="6"/>
-      <c r="Z109" s="6"/>
-      <c r="AA109" s="8"/>
-      <c r="AB109" s="8"/>
-      <c r="AC109" s="8"/>
-      <c r="AD109" s="8"/>
-      <c r="AE109" s="6"/>
+      <c r="O109" s="5">
+        <v>4617.7399999999998</v>
+      </c>
+      <c r="P109" s="5">
+        <v>4617.7399999999998</v>
+      </c>
+      <c r="Q109" s="6">
+        <v>-0.28350478673059321</v>
+      </c>
+      <c r="R109" s="7">
+        <v>43</v>
+      </c>
+      <c r="S109" s="6">
+        <v>-0.37681159420289856</v>
+      </c>
+      <c r="T109" s="6">
+        <v>0.020434238393673098</v>
+      </c>
+      <c r="U109" s="6">
+        <v>-0.29875653458185175</v>
+      </c>
+      <c r="V109" s="6">
+        <v>0.12578967200405394</v>
+      </c>
+      <c r="W109" s="6">
+        <v>0.08423687778003959</v>
+      </c>
+      <c r="X109" s="8">
+        <v>18.886670000000002</v>
+      </c>
+      <c r="Y109" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="8">
+        <v>4.0403093023255821</v>
+      </c>
+      <c r="AB109" s="8">
+        <v>3.96</v>
+      </c>
+      <c r="AC109" s="8">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="AD109" s="8">
+        <v>16.315000000000001</v>
+      </c>
+      <c r="AE109" s="6">
+        <v>1</v>
+      </c>
       <c r="AF109" s="9"/>
-      <c r="AG109" s="5"/>
+      <c r="AG109" s="5">
+        <v>0</v>
+      </c>
       <c r="AH109" s="10">
         <v>2</v>
       </c>
@@ -14285,7 +15327,7 @@
         <v>19735</v>
       </c>
       <c r="B111" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C111" s="4">
         <v>44</v>
@@ -14321,25 +15363,61 @@
       <c t="s" r="N111" s="4">
         <v>52</v>
       </c>
-      <c r="O111" s="5"/>
-      <c r="P111" s="5"/>
-      <c r="Q111" s="6"/>
-      <c r="R111" s="7"/>
-      <c r="S111" s="6"/>
-      <c r="T111" s="6"/>
-      <c r="U111" s="6"/>
-      <c r="V111" s="6"/>
-      <c r="W111" s="6"/>
-      <c r="X111" s="8"/>
-      <c r="Y111" s="6"/>
-      <c r="Z111" s="6"/>
-      <c r="AA111" s="8"/>
-      <c r="AB111" s="8"/>
-      <c r="AC111" s="8"/>
-      <c r="AD111" s="8"/>
-      <c r="AE111" s="6"/>
+      <c r="O111" s="5">
+        <v>369.5</v>
+      </c>
+      <c r="P111" s="5">
+        <v>369.5</v>
+      </c>
+      <c r="Q111" s="6">
+        <v>-0.78538155036418345</v>
+      </c>
+      <c r="R111" s="7">
+        <v>4</v>
+      </c>
+      <c r="S111" s="6">
+        <v>-0.81818181818181812</v>
+      </c>
+      <c r="T111" s="6">
+        <v>0.0074508795669824086</v>
+      </c>
+      <c r="U111" s="6">
+        <v>-0.28288741542625168</v>
+      </c>
+      <c r="V111" s="6">
+        <v>0.1586914749661705</v>
+      </c>
+      <c r="W111" s="6">
+        <v>-0.14163328822733423</v>
+      </c>
+      <c r="X111" s="8">
+        <v>20.875</v>
+      </c>
+      <c r="Y111" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="8">
+        <v>4.3875000000000002</v>
+      </c>
+      <c r="AB111" s="8">
+        <v>1.0083249999999999</v>
+      </c>
+      <c r="AC111" s="8">
+        <v>5.3958329999999997</v>
+      </c>
+      <c r="AD111" s="8">
+        <v>12.324999999999999</v>
+      </c>
+      <c r="AE111" s="6">
+        <v>1</v>
+      </c>
       <c r="AF111" s="9"/>
-      <c r="AG111" s="5"/>
+      <c r="AG111" s="5">
+        <v>0</v>
+      </c>
       <c r="AH111" s="10">
         <v>3</v>
       </c>
@@ -14602,7 +15680,7 @@
         <v>19740</v>
       </c>
       <c r="B114" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C114" s="4">
         <v>44</v>
@@ -14638,27 +15716,61 @@
       <c t="s" r="N114" s="4">
         <v>52</v>
       </c>
-      <c r="O114" s="5"/>
-      <c r="P114" s="5"/>
-      <c r="Q114" s="6"/>
-      <c r="R114" s="7"/>
-      <c r="S114" s="6"/>
-      <c r="T114" s="6"/>
-      <c r="U114" s="6"/>
-      <c r="V114" s="6"/>
-      <c r="W114" s="6"/>
-      <c r="X114" s="8"/>
-      <c r="Y114" s="6"/>
-      <c r="Z114" s="6"/>
-      <c r="AA114" s="8"/>
-      <c r="AB114" s="8"/>
+      <c r="O114" s="5">
+        <v>4768.3999999999996</v>
+      </c>
+      <c r="P114" s="5">
+        <v>4768.3999999999996</v>
+      </c>
+      <c r="Q114" s="6">
+        <v>0.35955658451467198</v>
+      </c>
+      <c r="R114" s="7">
+        <v>41</v>
+      </c>
+      <c r="S114" s="6">
+        <v>0.32258064516129026</v>
+      </c>
+      <c r="T114" s="6">
+        <v>0.42941508682157542</v>
+      </c>
+      <c r="U114" s="6">
+        <v>0.14482277074070968</v>
+      </c>
+      <c r="V114" s="6">
+        <v>0.033311802701115681</v>
+      </c>
+      <c r="W114" s="6">
+        <v>0.02307566479322205</v>
+      </c>
+      <c r="X114" s="8">
+        <v>24.991071428571427</v>
+      </c>
+      <c r="Y114" s="6">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="Z114" s="6">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AA114" s="8">
+        <v>4.4235780487804881</v>
+      </c>
+      <c r="AB114" s="8">
+        <v>2.9524703703703703</v>
+      </c>
       <c r="AC114" s="8">
         <v>8.0263570000000009</v>
       </c>
-      <c r="AD114" s="8"/>
-      <c r="AE114" s="6"/>
+      <c r="AD114" s="8">
+        <v>15.307142857142859</v>
+      </c>
+      <c r="AE114" s="6">
+        <v>0.6785714285714286</v>
+      </c>
       <c r="AF114" s="9"/>
-      <c r="AG114" s="5"/>
+      <c r="AG114" s="5">
+        <v>-196.19999999999999</v>
+      </c>
       <c r="AH114" s="10">
         <v>2</v>
       </c>
@@ -15445,7 +16557,7 @@
         <v>19752</v>
       </c>
       <c r="B121" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C121" s="4">
         <v>44</v>
@@ -15479,25 +16591,61 @@
       <c t="s" r="N121" s="4">
         <v>52</v>
       </c>
-      <c r="O121" s="5"/>
-      <c r="P121" s="5"/>
-      <c r="Q121" s="6"/>
-      <c r="R121" s="7"/>
-      <c r="S121" s="6"/>
-      <c r="T121" s="6"/>
-      <c r="U121" s="6"/>
-      <c r="V121" s="6"/>
-      <c r="W121" s="6"/>
-      <c r="X121" s="8"/>
-      <c r="Y121" s="6"/>
-      <c r="Z121" s="6"/>
-      <c r="AA121" s="8"/>
-      <c r="AB121" s="8"/>
-      <c r="AC121" s="8"/>
-      <c r="AD121" s="8"/>
-      <c r="AE121" s="6"/>
+      <c r="O121" s="5">
+        <v>2764.1500000000001</v>
+      </c>
+      <c r="P121" s="5">
+        <v>2764.1500000000001</v>
+      </c>
+      <c r="Q121" s="6">
+        <v>1.5245453964252769</v>
+      </c>
+      <c r="R121" s="7">
+        <v>28</v>
+      </c>
+      <c r="S121" s="6">
+        <v>1.7999999999999998</v>
+      </c>
+      <c r="T121" s="6">
+        <v>0</v>
+      </c>
+      <c r="U121" s="6">
+        <v>-0.28571170160808929</v>
+      </c>
+      <c r="V121" s="6">
+        <v>0.027033807861367869</v>
+      </c>
+      <c r="W121" s="6">
+        <v>-0.043903008158023261</v>
+      </c>
+      <c r="X121" s="8">
+        <v>20.103846153846156</v>
+      </c>
+      <c r="Y121" s="6">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="Z121" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA121" s="8">
+        <v>4.9964285714285719</v>
+      </c>
+      <c r="AB121" s="8">
+        <v>4.4359000000000002</v>
+      </c>
+      <c r="AC121" s="8">
+        <v>8.629486</v>
+      </c>
+      <c r="AD121" s="8">
+        <v>16.558976923076923</v>
+      </c>
+      <c r="AE121" s="6">
+        <v>1</v>
+      </c>
       <c r="AF121" s="9"/>
-      <c r="AG121" s="5"/>
+      <c r="AG121" s="5">
+        <v>0</v>
+      </c>
       <c r="AH121" s="10">
         <v>2</v>
       </c>
@@ -15983,10 +17131,10 @@
         <v>-0.22619047619047616</v>
       </c>
       <c r="T125" s="6">
-        <v>-0.0061469718726243766</v>
+        <v>0.11437165301123403</v>
       </c>
       <c r="U125" s="6">
-        <v>-0.31151693555198912</v>
+        <v>-0.1917289467015795</v>
       </c>
       <c r="V125" s="6">
         <v>0.069698137511614147</v>
@@ -16324,7 +17472,7 @@
         <v>19762</v>
       </c>
       <c r="B128" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C128" s="4">
         <v>44</v>
@@ -16360,27 +17508,61 @@
       <c t="s" r="N128" s="4">
         <v>52</v>
       </c>
-      <c r="O128" s="5"/>
-      <c r="P128" s="5"/>
-      <c r="Q128" s="6"/>
-      <c r="R128" s="7"/>
-      <c r="S128" s="6"/>
-      <c r="T128" s="6"/>
-      <c r="U128" s="6"/>
-      <c r="V128" s="6"/>
-      <c r="W128" s="6"/>
-      <c r="X128" s="8"/>
-      <c r="Y128" s="6"/>
-      <c r="Z128" s="6"/>
-      <c r="AA128" s="8"/>
-      <c r="AB128" s="8"/>
+      <c r="O128" s="5">
+        <v>2201.3000000000002</v>
+      </c>
+      <c r="P128" s="5">
+        <v>2201.3000000000002</v>
+      </c>
+      <c r="Q128" s="6">
+        <v>-0.20770947307803045</v>
+      </c>
+      <c r="R128" s="7">
+        <v>26</v>
+      </c>
+      <c r="S128" s="6">
+        <v>-0.23529411764705888</v>
+      </c>
+      <c r="T128" s="6">
+        <v>0</v>
+      </c>
+      <c r="U128" s="6">
+        <v>-0.31273338481806201</v>
+      </c>
+      <c r="V128" s="6">
+        <v>0.049641121155680736</v>
+      </c>
+      <c r="W128" s="6">
+        <v>-0.042604370144914361</v>
+      </c>
+      <c r="X128" s="8">
+        <v>27.104627777777779</v>
+      </c>
+      <c r="Y128" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z128" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AA128" s="8">
+        <v>7.3893320000000005</v>
+      </c>
+      <c r="AB128" s="8">
+        <v>8.2101833333333332</v>
+      </c>
       <c r="AC128" s="8">
-        <v>17.110783000000001</v>
-      </c>
-      <c r="AD128" s="8"/>
-      <c r="AE128" s="6"/>
+        <v>16.894444</v>
+      </c>
+      <c r="AD128" s="8">
+        <v>23.837038888888891</v>
+      </c>
+      <c r="AE128" s="6">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="AF128" s="9"/>
-      <c r="AG128" s="5"/>
+      <c r="AG128" s="5">
+        <v>-138.80000000000001</v>
+      </c>
       <c r="AH128" s="10">
         <v>2</v>
       </c>
@@ -16683,7 +17865,7 @@
         <v>19772</v>
       </c>
       <c r="B131" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C131" s="4">
         <v>44</v>
@@ -16719,25 +17901,59 @@
       <c t="s" r="N131" s="4">
         <v>52</v>
       </c>
-      <c r="O131" s="5"/>
-      <c r="P131" s="5"/>
-      <c r="Q131" s="6"/>
-      <c r="R131" s="7"/>
-      <c r="S131" s="6"/>
-      <c r="T131" s="6"/>
-      <c r="U131" s="6"/>
-      <c r="V131" s="6"/>
-      <c r="W131" s="6"/>
-      <c r="X131" s="8"/>
-      <c r="Y131" s="6"/>
+      <c r="O131" s="5">
+        <v>2691.5500000000002</v>
+      </c>
+      <c r="P131" s="5">
+        <v>2691.5500000000002</v>
+      </c>
+      <c r="Q131" s="6">
+        <v>-0.2140725556840346</v>
+      </c>
+      <c r="R131" s="7">
+        <v>30</v>
+      </c>
+      <c r="S131" s="6">
+        <v>-0.33333333333333337</v>
+      </c>
+      <c r="T131" s="6">
+        <v>0</v>
+      </c>
+      <c r="U131" s="6">
+        <v>-0.27403912243874345</v>
+      </c>
+      <c r="V131" s="6">
+        <v>0.077104085006780482</v>
+      </c>
+      <c r="W131" s="6">
+        <v>0.065445375341346063</v>
+      </c>
+      <c r="X131" s="8">
+        <v>30.193339999999999</v>
+      </c>
+      <c r="Y131" s="6">
+        <v>1</v>
+      </c>
       <c r="Z131" s="6"/>
-      <c r="AA131" s="8"/>
-      <c r="AB131" s="8"/>
-      <c r="AC131" s="8"/>
-      <c r="AD131" s="8"/>
-      <c r="AE131" s="6"/>
+      <c r="AA131" s="8">
+        <v>5.7953319999999993</v>
+      </c>
+      <c r="AB131" s="8">
+        <v>12.38334</v>
+      </c>
+      <c r="AC131" s="8">
+        <v>19.336110000000001</v>
+      </c>
+      <c r="AD131" s="8">
+        <v>24.759999999999998</v>
+      </c>
+      <c r="AE131" s="6">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="AF131" s="9"/>
-      <c r="AG131" s="5"/>
+      <c r="AG131" s="5">
+        <v>-82.400000000000006</v>
+      </c>
       <c r="AH131" s="10">
         <v>0</v>
       </c>
@@ -17249,7 +18465,9 @@
       <c r="AB135" s="8">
         <v>2.4788461538461539</v>
       </c>
-      <c r="AC135" s="8"/>
+      <c r="AC135" s="8">
+        <v>5.9076919999999999</v>
+      </c>
       <c r="AD135" s="8">
         <v>12.870511538461539</v>
       </c>
@@ -17507,7 +18725,9 @@
       <c r="AB137" s="8">
         <v>6.4566599999999994</v>
       </c>
-      <c r="AC137" s="8"/>
+      <c r="AC137" s="8">
+        <v>12.493332000000001</v>
+      </c>
       <c r="AD137" s="8">
         <v>19.399999999999999</v>
       </c>
@@ -18008,7 +19228,7 @@
         <v>19794</v>
       </c>
       <c r="B142" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C142" s="4">
         <v>44</v>
@@ -18042,25 +19262,61 @@
       <c t="s" r="N142" s="4">
         <v>52</v>
       </c>
-      <c r="O142" s="5"/>
-      <c r="P142" s="5"/>
-      <c r="Q142" s="6"/>
-      <c r="R142" s="7"/>
-      <c r="S142" s="6"/>
-      <c r="T142" s="6"/>
-      <c r="U142" s="6"/>
-      <c r="V142" s="6"/>
-      <c r="W142" s="6"/>
-      <c r="X142" s="8"/>
-      <c r="Y142" s="6"/>
-      <c r="Z142" s="6"/>
-      <c r="AA142" s="8"/>
-      <c r="AB142" s="8"/>
-      <c r="AC142" s="8"/>
-      <c r="AD142" s="8"/>
-      <c r="AE142" s="6"/>
+      <c r="O142" s="5">
+        <v>6233.1999999999998</v>
+      </c>
+      <c r="P142" s="5">
+        <v>6233.1999999999998</v>
+      </c>
+      <c r="Q142" s="6">
+        <v>-0.18489148799280253</v>
+      </c>
+      <c r="R142" s="7">
+        <v>60</v>
+      </c>
+      <c r="S142" s="6">
+        <v>-0.16666666666666663</v>
+      </c>
+      <c r="T142" s="6">
+        <v>0</v>
+      </c>
+      <c r="U142" s="6">
+        <v>-0.35793653340178405</v>
+      </c>
+      <c r="V142" s="6">
+        <v>0.044478117178977088</v>
+      </c>
+      <c r="W142" s="6">
+        <v>0.012783321568375795</v>
+      </c>
+      <c r="X142" s="8">
+        <v>24.873147222222222</v>
+      </c>
+      <c r="Y142" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="8">
+        <v>3.6155550000000001</v>
+      </c>
+      <c r="AB142" s="8">
+        <v>4.8328694444444444</v>
+      </c>
+      <c r="AC142" s="8">
+        <v>8.5601839999999996</v>
+      </c>
+      <c r="AD142" s="8">
+        <v>17.375925000000002</v>
+      </c>
+      <c r="AE142" s="6">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="AF142" s="9"/>
-      <c r="AG142" s="5"/>
+      <c r="AG142" s="5">
+        <v>0</v>
+      </c>
       <c r="AH142" s="10">
         <v>2</v>
       </c>
@@ -18361,7 +19617,7 @@
         <v>19804</v>
       </c>
       <c r="B145" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C145" s="4">
         <v>44</v>
@@ -18397,25 +19653,61 @@
       <c t="s" r="N145" s="4">
         <v>52</v>
       </c>
-      <c r="O145" s="5"/>
-      <c r="P145" s="5"/>
-      <c r="Q145" s="6"/>
-      <c r="R145" s="7"/>
-      <c r="S145" s="6"/>
-      <c r="T145" s="6"/>
-      <c r="U145" s="6"/>
-      <c r="V145" s="6"/>
-      <c r="W145" s="6"/>
-      <c r="X145" s="8"/>
-      <c r="Y145" s="6"/>
-      <c r="Z145" s="6"/>
-      <c r="AA145" s="8"/>
-      <c r="AB145" s="8"/>
-      <c r="AC145" s="8"/>
-      <c r="AD145" s="8"/>
-      <c r="AE145" s="6"/>
+      <c r="O145" s="5">
+        <v>3171.0100000000002</v>
+      </c>
+      <c r="P145" s="5">
+        <v>3171.0100000000002</v>
+      </c>
+      <c r="Q145" s="6">
+        <v>0.035891857281927786</v>
+      </c>
+      <c r="R145" s="7">
+        <v>41</v>
+      </c>
+      <c r="S145" s="6">
+        <v>0.078947368421052655</v>
+      </c>
+      <c r="T145" s="6">
+        <v>0.59040201702296735</v>
+      </c>
+      <c r="U145" s="6">
+        <v>0.26924566620729673</v>
+      </c>
+      <c r="V145" s="6">
+        <v>0.063681603022380878</v>
+      </c>
+      <c r="W145" s="6">
+        <v>-0.00072689773920612047</v>
+      </c>
+      <c r="X145" s="8">
+        <v>19.149020588235292</v>
+      </c>
+      <c r="Y145" s="6">
+        <v>0.47058823529411764</v>
+      </c>
+      <c r="Z145" s="6">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AA145" s="8">
+        <v>4.7418707317073165</v>
+      </c>
+      <c r="AB145" s="8">
+        <v>5.5236124999999996</v>
+      </c>
+      <c r="AC145" s="8">
+        <v>10.436845999999999</v>
+      </c>
+      <c r="AD145" s="8">
+        <v>14.576961764705882</v>
+      </c>
+      <c r="AE145" s="6">
+        <v>0.88235294117647056</v>
+      </c>
       <c r="AF145" s="9"/>
-      <c r="AG145" s="5"/>
+      <c r="AG145" s="5">
+        <v>0</v>
+      </c>
       <c r="AH145" s="10">
         <v>1</v>
       </c>
@@ -18534,7 +19826,9 @@
       <c r="AB146" s="8">
         <v>3.87615</v>
       </c>
-      <c r="AC146" s="8"/>
+      <c r="AC146" s="8">
+        <v>6.965414</v>
+      </c>
       <c r="AD146" s="8">
         <v>12.892815517241381</v>
       </c>
@@ -18718,7 +20012,7 @@
         <v>19809</v>
       </c>
       <c r="B148" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C148" s="4">
         <v>44</v>
@@ -18754,25 +20048,61 @@
       <c t="s" r="N148" s="4">
         <v>52</v>
       </c>
-      <c r="O148" s="5"/>
-      <c r="P148" s="5"/>
-      <c r="Q148" s="6"/>
-      <c r="R148" s="7"/>
-      <c r="S148" s="6"/>
-      <c r="T148" s="6"/>
-      <c r="U148" s="6"/>
-      <c r="V148" s="6"/>
-      <c r="W148" s="6"/>
-      <c r="X148" s="8"/>
-      <c r="Y148" s="6"/>
-      <c r="Z148" s="6"/>
-      <c r="AA148" s="8"/>
-      <c r="AB148" s="8"/>
-      <c r="AC148" s="8"/>
-      <c r="AD148" s="8"/>
-      <c r="AE148" s="6"/>
+      <c r="O148" s="5">
+        <v>4982.5299999999997</v>
+      </c>
+      <c r="P148" s="5">
+        <v>4982.5299999999997</v>
+      </c>
+      <c r="Q148" s="6">
+        <v>-0.53590097541710446</v>
+      </c>
+      <c r="R148" s="7">
+        <v>62</v>
+      </c>
+      <c r="S148" s="6">
+        <v>-0.48333333333333328</v>
+      </c>
+      <c r="T148" s="6">
+        <v>0</v>
+      </c>
+      <c r="U148" s="6">
+        <v>-0.3025149873658563</v>
+      </c>
+      <c r="V148" s="6">
+        <v>0.074418217251075267</v>
+      </c>
+      <c r="W148" s="6">
+        <v>0.033463120141775361</v>
+      </c>
+      <c r="X148" s="8">
+        <v>31.065985714285716</v>
+      </c>
+      <c r="Y148" s="6">
+        <v>0.53061224489795922</v>
+      </c>
+      <c r="Z148" s="6">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="AA148" s="8">
+        <v>6.1789062499999998</v>
+      </c>
+      <c r="AB148" s="8">
+        <v>6.8307026315789479</v>
+      </c>
+      <c r="AC148" s="8">
+        <v>13.378499</v>
+      </c>
+      <c r="AD148" s="8">
+        <v>19.017729787234043</v>
+      </c>
+      <c r="AE148" s="6">
+        <v>0.81632653061224492</v>
+      </c>
       <c r="AF148" s="9"/>
-      <c r="AG148" s="5"/>
+      <c r="AG148" s="5">
+        <v>-11.83</v>
+      </c>
       <c r="AH148" s="10">
         <v>2</v>
       </c>
@@ -18813,7 +20143,7 @@
         <v>19817</v>
       </c>
       <c r="B149" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C149" s="4">
         <v>44</v>
@@ -18849,25 +20179,61 @@
       <c t="s" r="N149" s="4">
         <v>52</v>
       </c>
-      <c r="O149" s="5"/>
-      <c r="P149" s="5"/>
-      <c r="Q149" s="6"/>
-      <c r="R149" s="7"/>
-      <c r="S149" s="6"/>
-      <c r="T149" s="6"/>
-      <c r="U149" s="6"/>
-      <c r="V149" s="6"/>
-      <c r="W149" s="6"/>
-      <c r="X149" s="8"/>
-      <c r="Y149" s="6"/>
-      <c r="Z149" s="6"/>
-      <c r="AA149" s="8"/>
-      <c r="AB149" s="8"/>
-      <c r="AC149" s="8"/>
-      <c r="AD149" s="8"/>
-      <c r="AE149" s="6"/>
+      <c r="O149" s="5">
+        <v>3085.5799999999999</v>
+      </c>
+      <c r="P149" s="5">
+        <v>3085.5799999999999</v>
+      </c>
+      <c r="Q149" s="6">
+        <v>-0.42131233320142614</v>
+      </c>
+      <c r="R149" s="7">
+        <v>36</v>
+      </c>
+      <c r="S149" s="6">
+        <v>-0.32075471698113212</v>
+      </c>
+      <c r="T149" s="6">
+        <v>0.3951407839044847</v>
+      </c>
+      <c r="U149" s="6">
+        <v>-0.0086115090193739918</v>
+      </c>
+      <c r="V149" s="6">
+        <v>0.043010066178805935</v>
+      </c>
+      <c r="W149" s="6">
+        <v>-0.034699797120800631</v>
+      </c>
+      <c r="X149" s="8">
+        <v>33.398414285714288</v>
+      </c>
+      <c r="Y149" s="6">
+        <v>0.52380952380952384</v>
+      </c>
+      <c r="Z149" s="6">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="AA149" s="8">
+        <v>6.8680555555555554</v>
+      </c>
+      <c r="AB149" s="8">
+        <v>8.2563476190476184</v>
+      </c>
+      <c r="AC149" s="8">
+        <v>14.958621000000001</v>
+      </c>
+      <c r="AD149" s="8">
+        <v>21.996823809523807</v>
+      </c>
+      <c r="AE149" s="6">
+        <v>0.47619047619047616</v>
+      </c>
       <c r="AF149" s="9"/>
-      <c r="AG149" s="5"/>
+      <c r="AG149" s="5">
+        <v>0</v>
+      </c>
       <c r="AH149" s="10">
         <v>2</v>
       </c>
@@ -19039,7 +20405,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -19075,25 +20441,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>2397.2800000000002</v>
+      </c>
+      <c r="P151" s="5">
+        <v>2397.2800000000002</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.50596400985895751</v>
+      </c>
+      <c r="R151" s="7">
+        <v>42</v>
+      </c>
+      <c r="S151" s="6">
+        <v>-0.023255813953488413</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.29884264666622168</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.030009218781285454</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.063544517119401983</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.0078730895014349593</v>
+      </c>
+      <c r="X151" s="8">
+        <v>25.938332500000001</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>4.5622222222222222</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>4.2364026315789474</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>8.6351829999999996</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>15.2720825</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.75</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -19398,7 +20800,7 @@
         <v>19843</v>
       </c>
       <c r="B154" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C154" s="4">
         <v>44</v>
@@ -19434,25 +20836,57 @@
       <c t="s" r="N154" s="4">
         <v>52</v>
       </c>
-      <c r="O154" s="5"/>
-      <c r="P154" s="5"/>
+      <c r="O154" s="5">
+        <v>2857.7800000000002</v>
+      </c>
+      <c r="P154" s="5">
+        <v>2857.7800000000002</v>
+      </c>
       <c r="Q154" s="6"/>
-      <c r="R154" s="7"/>
+      <c r="R154" s="7">
+        <v>27</v>
+      </c>
       <c r="S154" s="6"/>
-      <c r="T154" s="6"/>
-      <c r="U154" s="6"/>
-      <c r="V154" s="6"/>
-      <c r="W154" s="6"/>
-      <c r="X154" s="8"/>
-      <c r="Y154" s="6"/>
-      <c r="Z154" s="6"/>
-      <c r="AA154" s="8"/>
-      <c r="AB154" s="8"/>
-      <c r="AC154" s="8"/>
-      <c r="AD154" s="8"/>
-      <c r="AE154" s="6"/>
+      <c r="T154" s="6">
+        <v>0.28124358767994734</v>
+      </c>
+      <c r="U154" s="6">
+        <v>-0.016991405916480622</v>
+      </c>
+      <c r="V154" s="6">
+        <v>0.018126307833353162</v>
+      </c>
+      <c r="W154" s="6">
+        <v>-0.022065729342356653</v>
+      </c>
+      <c r="X154" s="8">
+        <v>19.964099999999998</v>
+      </c>
+      <c r="Y154" s="6">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Z154" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA154" s="8">
+        <v>1.2854166666666667</v>
+      </c>
+      <c r="AB154" s="8">
+        <v>1.425</v>
+      </c>
+      <c r="AC154" s="8">
+        <v>2.4416660000000001</v>
+      </c>
+      <c r="AD154" s="8">
+        <v>10.917946153846154</v>
+      </c>
+      <c r="AE154" s="6">
+        <v>1</v>
+      </c>
       <c r="AF154" s="9"/>
-      <c r="AG154" s="5"/>
+      <c r="AG154" s="5">
+        <v>1.7</v>
+      </c>
       <c r="AH154" s="10">
         <v>2</v>
       </c>
@@ -19700,7 +21134,9 @@
       <c r="AB156" s="8">
         <v>5.8435483870967744</v>
       </c>
-      <c r="AC156" s="8"/>
+      <c r="AC156" s="8">
+        <v>11.979569</v>
+      </c>
       <c r="AD156" s="8">
         <v>18.443750000000001</v>
       </c>
@@ -19941,7 +21377,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>44</v>
@@ -19977,25 +21413,61 @@
       <c t="s" r="N159" s="4">
         <v>52</v>
       </c>
-      <c r="O159" s="5"/>
-      <c r="P159" s="5"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="7"/>
-      <c r="S159" s="6"/>
-      <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6"/>
-      <c r="X159" s="8"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="6"/>
-      <c r="AA159" s="8"/>
-      <c r="AB159" s="8"/>
-      <c r="AC159" s="8"/>
-      <c r="AD159" s="8"/>
-      <c r="AE159" s="6"/>
+      <c r="O159" s="5">
+        <v>7111.5100000000002</v>
+      </c>
+      <c r="P159" s="5">
+        <v>7111.5100000000002</v>
+      </c>
+      <c r="Q159" s="6">
+        <v>-0.13320567794275728</v>
+      </c>
+      <c r="R159" s="7">
+        <v>71</v>
+      </c>
+      <c r="S159" s="6">
+        <v>-0.18390804597701149</v>
+      </c>
+      <c r="T159" s="6">
+        <v>0.3030912844107651</v>
+      </c>
+      <c r="U159" s="6">
+        <v>-0.0073195847295440767</v>
+      </c>
+      <c r="V159" s="6">
+        <v>0.044212199659425355</v>
+      </c>
+      <c r="W159" s="6">
+        <v>0.011362636064633249</v>
+      </c>
+      <c r="X159" s="8">
+        <v>30.589285714285715</v>
+      </c>
+      <c r="Y159" s="6">
+        <v>0.4107142857142857</v>
+      </c>
+      <c r="Z159" s="6">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AA159" s="8">
+        <v>6.1208333333333336</v>
+      </c>
+      <c r="AB159" s="8">
+        <v>6.2744053571428564</v>
+      </c>
+      <c r="AC159" s="8">
+        <v>13.012123000000001</v>
+      </c>
+      <c r="AD159" s="8">
+        <v>19.90267857142857</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>0.42857142857142855</v>
+      </c>
       <c r="AF159" s="9"/>
-      <c r="AG159" s="5"/>
+      <c r="AG159" s="5">
+        <v>-41.899999999999999</v>
+      </c>
       <c r="AH159" s="10">
         <v>2</v>
       </c>
@@ -20278,7 +21750,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
@@ -20314,25 +21786,61 @@
       <c t="s" r="N162" s="4">
         <v>52</v>
       </c>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="6"/>
-      <c r="T162" s="6"/>
-      <c r="U162" s="6"/>
-      <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
-      <c r="X162" s="8"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="6"/>
-      <c r="AA162" s="8"/>
-      <c r="AB162" s="8"/>
-      <c r="AC162" s="8"/>
-      <c r="AD162" s="8"/>
-      <c r="AE162" s="6"/>
+      <c r="O162" s="5">
+        <v>4216.21</v>
+      </c>
+      <c r="P162" s="5">
+        <v>4216.21</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>-0.30461379619733731</v>
+      </c>
+      <c r="R162" s="7">
+        <v>48</v>
+      </c>
+      <c r="S162" s="6">
+        <v>-0.36842105263157898</v>
+      </c>
+      <c r="T162" s="6">
+        <v>0.32650458587214587</v>
+      </c>
+      <c r="U162" s="6">
+        <v>-0.0099421281198042791</v>
+      </c>
+      <c r="V162" s="6">
+        <v>0.046817520948909092</v>
+      </c>
+      <c r="W162" s="6">
+        <v>0.028002044490193799</v>
+      </c>
+      <c r="X162" s="8">
+        <v>25.573335</v>
+      </c>
+      <c r="Y162" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>10.232954545454545</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>5.2481499999999999</v>
+      </c>
+      <c r="AC162" s="8">
+        <v>15.249814000000001</v>
+      </c>
+      <c r="AD162" s="8">
+        <v>21.7225</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF162" s="9"/>
-      <c r="AG162" s="5"/>
+      <c r="AG162" s="5">
+        <v>-293.60000000000002</v>
+      </c>
       <c r="AH162" s="10">
         <v>2</v>
       </c>
@@ -21254,7 +22762,7 @@
         <v>19888</v>
       </c>
       <c r="B170" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C170" s="4">
         <v>44</v>
@@ -21290,25 +22798,61 @@
       <c t="s" r="N170" s="4">
         <v>52</v>
       </c>
-      <c r="O170" s="5"/>
-      <c r="P170" s="5"/>
-      <c r="Q170" s="6"/>
-      <c r="R170" s="7"/>
-      <c r="S170" s="6"/>
-      <c r="T170" s="6"/>
-      <c r="U170" s="6"/>
-      <c r="V170" s="6"/>
-      <c r="W170" s="6"/>
-      <c r="X170" s="8"/>
-      <c r="Y170" s="6"/>
-      <c r="Z170" s="6"/>
-      <c r="AA170" s="8"/>
-      <c r="AB170" s="8"/>
-      <c r="AC170" s="8"/>
-      <c r="AD170" s="8"/>
-      <c r="AE170" s="6"/>
+      <c r="O170" s="5">
+        <v>3964.0599999999999</v>
+      </c>
+      <c r="P170" s="5">
+        <v>3964.0599999999999</v>
+      </c>
+      <c r="Q170" s="6">
+        <v>0.16802993694383872</v>
+      </c>
+      <c r="R170" s="7">
+        <v>38</v>
+      </c>
+      <c r="S170" s="6">
+        <v>0.085714285714285632</v>
+      </c>
+      <c r="T170" s="6">
+        <v>0.29457856339207783</v>
+      </c>
+      <c r="U170" s="6">
+        <v>-0.0028462989964834033</v>
+      </c>
+      <c r="V170" s="6">
+        <v>0.029595793201919247</v>
+      </c>
+      <c r="W170" s="6">
+        <v>-0.0084611484185405875</v>
+      </c>
+      <c r="X170" s="8">
+        <v>23.07047714285714</v>
+      </c>
+      <c r="Y170" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z170" s="6">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="AA170" s="8">
+        <v>5.3416657894736845</v>
+      </c>
+      <c r="AB170" s="8">
+        <v>3.7576199999999997</v>
+      </c>
+      <c r="AC170" s="8">
+        <v>9.1299989999999998</v>
+      </c>
+      <c r="AD170" s="8">
+        <v>16.060951428571428</v>
+      </c>
+      <c r="AE170" s="6">
+        <v>0.91428571428571426</v>
+      </c>
       <c r="AF170" s="9"/>
-      <c r="AG170" s="5"/>
+      <c r="AG170" s="5">
+        <v>0</v>
+      </c>
       <c r="AH170" s="10">
         <v>4</v>
       </c>
@@ -21873,7 +23417,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>44</v>
@@ -21909,25 +23453,61 @@
       <c t="s" r="N175" s="4">
         <v>52</v>
       </c>
-      <c r="O175" s="5"/>
-      <c r="P175" s="5"/>
-      <c r="Q175" s="6"/>
-      <c r="R175" s="7"/>
-      <c r="S175" s="6"/>
-      <c r="T175" s="6"/>
-      <c r="U175" s="6"/>
-      <c r="V175" s="6"/>
-      <c r="W175" s="6"/>
-      <c r="X175" s="8"/>
-      <c r="Y175" s="6"/>
-      <c r="Z175" s="6"/>
-      <c r="AA175" s="8"/>
-      <c r="AB175" s="8"/>
-      <c r="AC175" s="8"/>
-      <c r="AD175" s="8"/>
-      <c r="AE175" s="6"/>
+      <c r="O175" s="5">
+        <v>2090.8000000000002</v>
+      </c>
+      <c r="P175" s="5">
+        <v>2090.8000000000002</v>
+      </c>
+      <c r="Q175" s="6">
+        <v>-0.20951844444360412</v>
+      </c>
+      <c r="R175" s="7">
+        <v>39</v>
+      </c>
+      <c r="S175" s="6">
+        <v>0.11428571428571432</v>
+      </c>
+      <c r="T175" s="6">
+        <v>-0.0029596326764874687</v>
+      </c>
+      <c r="U175" s="6">
+        <v>-0.43385689688157636</v>
+      </c>
+      <c r="V175" s="6">
+        <v>0.03887602831452075</v>
+      </c>
+      <c r="W175" s="6">
+        <v>-0.017537784580065045</v>
+      </c>
+      <c r="X175" s="8">
+        <v>33.680299999999995</v>
+      </c>
+      <c r="Y175" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z175" s="6">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="AA175" s="8">
+        <v>10.411459375</v>
+      </c>
+      <c r="AB175" s="8">
+        <v>2.2742454545454547</v>
+      </c>
+      <c r="AC175" s="8">
+        <v>15.371211000000001</v>
+      </c>
+      <c r="AD175" s="8">
+        <v>22.325754545454547</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>0.27272727272727271</v>
+      </c>
       <c r="AF175" s="9"/>
-      <c r="AG175" s="5"/>
+      <c r="AG175" s="5">
+        <v>-280.69999999999999</v>
+      </c>
       <c r="AH175" s="10">
         <v>2</v>
       </c>
@@ -22175,7 +23755,9 @@
       <c r="AB177" s="8">
         <v>1.6941176470588235</v>
       </c>
-      <c r="AC177" s="8"/>
+      <c r="AC177" s="8">
+        <v>4.8894869999999999</v>
+      </c>
       <c r="AD177" s="8">
         <v>11.844117647058823</v>
       </c>
@@ -22433,7 +24015,9 @@
       <c r="AB179" s="8">
         <v>17.006249999999998</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>22.354861</v>
+      </c>
       <c r="AD179" s="8">
         <v>29.324304166666668</v>
       </c>
@@ -22482,7 +24066,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>44</v>
@@ -22518,25 +24102,61 @@
       <c t="s" r="N180" s="4">
         <v>52</v>
       </c>
-      <c r="O180" s="5"/>
-      <c r="P180" s="5"/>
-      <c r="Q180" s="6"/>
-      <c r="R180" s="7"/>
-      <c r="S180" s="6"/>
-      <c r="T180" s="6"/>
-      <c r="U180" s="6"/>
-      <c r="V180" s="6"/>
-      <c r="W180" s="6"/>
-      <c r="X180" s="8"/>
-      <c r="Y180" s="6"/>
-      <c r="Z180" s="6"/>
-      <c r="AA180" s="8"/>
-      <c r="AB180" s="8"/>
-      <c r="AC180" s="8"/>
-      <c r="AD180" s="8"/>
-      <c r="AE180" s="6"/>
+      <c r="O180" s="5">
+        <v>1635.6500000000001</v>
+      </c>
+      <c r="P180" s="5">
+        <v>1635.6500000000001</v>
+      </c>
+      <c r="Q180" s="6">
+        <v>-0.4746756166495375</v>
+      </c>
+      <c r="R180" s="7">
+        <v>22</v>
+      </c>
+      <c r="S180" s="6">
+        <v>-0.47619047619047616</v>
+      </c>
+      <c r="T180" s="6">
+        <v>0</v>
+      </c>
+      <c r="U180" s="6">
+        <v>-0.34574022559838596</v>
+      </c>
+      <c r="V180" s="6">
+        <v>0.25226148625928529</v>
+      </c>
+      <c r="W180" s="6">
+        <v>0.11297129581511936</v>
+      </c>
+      <c r="X180" s="8">
+        <v>31.072222222222219</v>
+      </c>
+      <c r="Y180" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z180" s="6">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AA180" s="8">
+        <v>5.3999999999999995</v>
+      </c>
+      <c r="AB180" s="8">
+        <v>15.135188888888889</v>
+      </c>
+      <c r="AC180" s="8">
+        <v>20.616665999999999</v>
+      </c>
+      <c r="AD180" s="8">
+        <v>28.544444444444441</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>0.77777777777777779</v>
+      </c>
       <c r="AF180" s="9"/>
-      <c r="AG180" s="5"/>
+      <c r="AG180" s="5">
+        <v>-143.80000000000001</v>
+      </c>
       <c r="AH180" s="10">
         <v>2</v>
       </c>
@@ -23194,7 +24814,7 @@
         <v>19926</v>
       </c>
       <c r="B186" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C186" s="4">
         <v>44</v>
@@ -23230,25 +24850,61 @@
       <c t="s" r="N186" s="4">
         <v>52</v>
       </c>
-      <c r="O186" s="5"/>
-      <c r="P186" s="5"/>
-      <c r="Q186" s="6"/>
-      <c r="R186" s="7"/>
-      <c r="S186" s="6"/>
-      <c r="T186" s="6"/>
-      <c r="U186" s="6"/>
-      <c r="V186" s="6"/>
-      <c r="W186" s="6"/>
-      <c r="X186" s="8"/>
-      <c r="Y186" s="6"/>
-      <c r="Z186" s="6"/>
-      <c r="AA186" s="8"/>
-      <c r="AB186" s="8"/>
-      <c r="AC186" s="8"/>
-      <c r="AD186" s="8"/>
-      <c r="AE186" s="6"/>
+      <c r="O186" s="5">
+        <v>1774.5</v>
+      </c>
+      <c r="P186" s="5">
+        <v>1774.5</v>
+      </c>
+      <c r="Q186" s="6">
+        <v>-0.32992221131334487</v>
+      </c>
+      <c r="R186" s="7">
+        <v>19</v>
+      </c>
+      <c r="S186" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="T186" s="6">
+        <v>0.74428841927303468</v>
+      </c>
+      <c r="U186" s="6">
+        <v>0.44005060580445199</v>
+      </c>
+      <c r="V186" s="6">
+        <v>0.12276838546069314</v>
+      </c>
+      <c r="W186" s="6">
+        <v>0.057386587771203153</v>
+      </c>
+      <c r="X186" s="8">
+        <v>28.316666666666666</v>
+      </c>
+      <c r="Y186" s="6">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="Z186" s="6">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AA186" s="8">
+        <v>10.379826315789474</v>
+      </c>
+      <c r="AB186" s="8">
+        <v>5.9722222222222223</v>
+      </c>
+      <c r="AC186" s="8">
+        <v>16.442222000000001</v>
+      </c>
+      <c r="AD186" s="8">
+        <v>22.918522222222222</v>
+      </c>
+      <c r="AE186" s="6">
+        <v>0.55555555555555558</v>
+      </c>
       <c r="AF186" s="9"/>
-      <c r="AG186" s="5"/>
+      <c r="AG186" s="5">
+        <v>-162.69999999999999</v>
+      </c>
       <c r="AH186" s="10">
         <v>2</v>
       </c>
@@ -23289,7 +24945,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -23325,25 +24981,61 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
-      <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="O187" s="5">
+        <v>1299.1199999999999</v>
+      </c>
+      <c r="P187" s="5">
+        <v>1299.1199999999999</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>-0.15487900078064021</v>
+      </c>
+      <c r="R187" s="7">
+        <v>18</v>
+      </c>
+      <c r="S187" s="6">
+        <v>-0.1428571428571429</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.32619003633228649</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.23305121928690192</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.10890564382043232</v>
+      </c>
+      <c r="X187" s="8">
+        <v>42.352220000000003</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>9.1518500000000014</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>14.85778</v>
+      </c>
+      <c r="AC187" s="8">
+        <v>23.724443000000001</v>
+      </c>
+      <c r="AD187" s="8">
+        <v>30.658886666666668</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.066666666666666666</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>0</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -23517,7 +25209,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -23553,25 +25245,61 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
-      <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="O189" s="5">
+        <v>5125.0200000000004</v>
+      </c>
+      <c r="P189" s="5">
+        <v>5125.0200000000004</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.32731275251217262</v>
+      </c>
+      <c r="R189" s="7">
+        <v>91</v>
+      </c>
+      <c r="S189" s="6">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="T189" s="6">
+        <v>0.25939494870263918</v>
+      </c>
+      <c r="U189" s="6">
+        <v>-0.0061669417875442429</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.042825198730931775</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.011566784129622908</v>
+      </c>
+      <c r="X189" s="8">
+        <v>29.79382716049383</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.1728395061728395</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.19753086419753085</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>5.740502150537635</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>14.130701315789473</v>
+      </c>
+      <c r="AC189" s="8">
+        <v>19.625968</v>
+      </c>
+      <c r="AD189" s="8">
+        <v>25.424074074074074</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.65432098765432101</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>0</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -23612,7 +25340,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -23648,25 +25376,61 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
-      <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="O190" s="5">
+        <v>3208.27</v>
+      </c>
+      <c r="P190" s="5">
+        <v>3208.27</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>0.027945723394370514</v>
+      </c>
+      <c r="R190" s="7">
+        <v>33</v>
+      </c>
+      <c r="S190" s="6">
+        <v>-0.25</v>
+      </c>
+      <c r="T190" s="6">
+        <v>1.3229545206606677</v>
+      </c>
+      <c r="U190" s="6">
+        <v>0.85700246550321513</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.067338160441608716</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.032736957924364221</v>
+      </c>
+      <c r="X190" s="8">
+        <v>22.876666666666665</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>4.663636363636364</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>4.4500000000000002</v>
+      </c>
+      <c r="AC190" s="8">
+        <v>8.467708</v>
+      </c>
+      <c r="AD190" s="8">
+        <v>15.475553333333332</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.8666666666666667</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>0</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -24098,7 +25862,7 @@
         <v>19943</v>
       </c>
       <c r="B194" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C194" s="4">
         <v>44</v>
@@ -24134,25 +25898,61 @@
       <c t="s" r="N194" s="4">
         <v>52</v>
       </c>
-      <c r="O194" s="5"/>
-      <c r="P194" s="5"/>
-      <c r="Q194" s="6"/>
-      <c r="R194" s="7"/>
-      <c r="S194" s="6"/>
-      <c r="T194" s="6"/>
-      <c r="U194" s="6"/>
-      <c r="V194" s="6"/>
-      <c r="W194" s="6"/>
-      <c r="X194" s="8"/>
-      <c r="Y194" s="6"/>
-      <c r="Z194" s="6"/>
-      <c r="AA194" s="8"/>
-      <c r="AB194" s="8"/>
-      <c r="AC194" s="8"/>
-      <c r="AD194" s="8"/>
-      <c r="AE194" s="6"/>
+      <c r="O194" s="5">
+        <v>1603.2</v>
+      </c>
+      <c r="P194" s="5">
+        <v>1603.2</v>
+      </c>
+      <c r="Q194" s="6">
+        <v>-0.25272676423976881</v>
+      </c>
+      <c r="R194" s="7">
+        <v>21</v>
+      </c>
+      <c r="S194" s="6">
+        <v>-0.36363636363636365</v>
+      </c>
+      <c r="T194" s="6">
+        <v>0.44881992265469062</v>
+      </c>
+      <c r="U194" s="6">
+        <v>0.048464383732534928</v>
+      </c>
+      <c r="V194" s="6">
+        <v>0.34046594311377248</v>
+      </c>
+      <c r="W194" s="6">
+        <v>0.11748690119760478</v>
+      </c>
+      <c r="X194" s="8">
+        <v>26.216669230769234</v>
+      </c>
+      <c r="Y194" s="6">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Z194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA194" s="8">
+        <v>7.1015136363636371</v>
+      </c>
+      <c r="AB194" s="8">
+        <v>6.5972250000000008</v>
+      </c>
+      <c r="AC194" s="8">
+        <v>14.35876</v>
+      </c>
+      <c r="AD194" s="8">
+        <v>20.661538461538463</v>
+      </c>
+      <c r="AE194" s="6">
+        <v>0.61538461538461542</v>
+      </c>
       <c r="AF194" s="9"/>
-      <c r="AG194" s="5"/>
+      <c r="AG194" s="5">
+        <v>-48.899999999999999</v>
+      </c>
       <c r="AH194" s="10">
         <v>2</v>
       </c>
@@ -24193,7 +25993,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -24229,25 +26029,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>3928.1900000000001</v>
+      </c>
+      <c r="P195" s="5">
+        <v>3928.1900000000001</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>-0.25722038385175383</v>
+      </c>
+      <c r="R195" s="7">
+        <v>49</v>
+      </c>
+      <c r="S195" s="6">
+        <v>-0.30000000000000004</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.32613638851481219</v>
+      </c>
+      <c r="U195" s="6">
+        <v>-0.02865551309890815</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.030767987291857063</v>
+      </c>
+      <c r="W195" s="6">
+        <v>0.00014065001947461808</v>
+      </c>
+      <c r="X195" s="8">
+        <v>31.200506060606063</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0.12121212121212122</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>4.9840270833333333</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>11.046969696969697</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>23.573736363636364</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.48484848484848486</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>0</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>
@@ -24812,7 +26646,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>44</v>
@@ -24848,25 +26682,61 @@
       <c t="s" r="N200" s="4">
         <v>52</v>
       </c>
-      <c r="O200" s="5"/>
-      <c r="P200" s="5"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
-      <c r="W200" s="6"/>
-      <c r="X200" s="8"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6"/>
-      <c r="AA200" s="8"/>
-      <c r="AB200" s="8"/>
-      <c r="AC200" s="8"/>
-      <c r="AD200" s="8"/>
-      <c r="AE200" s="6"/>
+      <c r="O200" s="5">
+        <v>1433.5899999999999</v>
+      </c>
+      <c r="P200" s="5">
+        <v>1433.5899999999999</v>
+      </c>
+      <c r="Q200" s="6">
+        <v>0.39199712587874291</v>
+      </c>
+      <c r="R200" s="7">
+        <v>17</v>
+      </c>
+      <c r="S200" s="6">
+        <v>0.41666666666666674</v>
+      </c>
+      <c r="T200" s="6">
+        <v>0.48171192600394819</v>
+      </c>
+      <c r="U200" s="6">
+        <v>0.081981180114258617</v>
+      </c>
+      <c r="V200" s="6">
+        <v>0.15514163742771644</v>
+      </c>
+      <c r="W200" s="6">
+        <v>0.084193876910413717</v>
+      </c>
+      <c r="X200" s="8">
+        <v>31.918181818181822</v>
+      </c>
+      <c r="Y200" s="6">
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="Z200" s="6">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="AA200" s="8">
+        <v>10.299017647058823</v>
+      </c>
+      <c r="AB200" s="8">
+        <v>9.0499999999999989</v>
+      </c>
+      <c r="AC200" s="8">
+        <v>18.775756999999999</v>
+      </c>
+      <c r="AD200" s="8">
+        <v>25.722727272727273</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0.36363636363636365</v>
+      </c>
       <c r="AF200" s="9"/>
-      <c r="AG200" s="5"/>
+      <c r="AG200" s="5">
+        <v>0</v>
+      </c>
       <c r="AH200" s="10">
         <v>3</v>
       </c>
@@ -25302,7 +27172,9 @@
       <c r="AB204" s="8">
         <v>5.2717923076923077</v>
       </c>
-      <c r="AC204" s="8"/>
+      <c r="AC204" s="8">
+        <v>11.615126999999999</v>
+      </c>
       <c r="AD204" s="8">
         <v>17.784521428571431</v>
       </c>
@@ -25480,7 +27352,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>44</v>
@@ -25516,25 +27388,57 @@
       <c t="s" r="N206" s="4">
         <v>52</v>
       </c>
-      <c r="O206" s="5"/>
-      <c r="P206" s="5"/>
+      <c r="O206" s="5">
+        <v>2598.5999999999999</v>
+      </c>
+      <c r="P206" s="5">
+        <v>2598.5999999999999</v>
+      </c>
       <c r="Q206" s="6"/>
-      <c r="R206" s="7"/>
+      <c r="R206" s="7">
+        <v>28</v>
+      </c>
       <c r="S206" s="6"/>
-      <c r="T206" s="6"/>
-      <c r="U206" s="6"/>
-      <c r="V206" s="6"/>
-      <c r="W206" s="6"/>
-      <c r="X206" s="8"/>
-      <c r="Y206" s="6"/>
-      <c r="Z206" s="6"/>
-      <c r="AA206" s="8"/>
-      <c r="AB206" s="8"/>
-      <c r="AC206" s="8"/>
-      <c r="AD206" s="8"/>
-      <c r="AE206" s="6"/>
+      <c r="T206" s="6">
+        <v>0.37734980374047566</v>
+      </c>
+      <c r="U206" s="6">
+        <v>0.014843069345031939</v>
+      </c>
+      <c r="V206" s="6">
+        <v>0.078537866543523446</v>
+      </c>
+      <c r="W206" s="6">
+        <v>0.059746979142615259</v>
+      </c>
+      <c r="X206" s="8">
+        <v>43.260418749999999</v>
+      </c>
+      <c r="Y206" s="6">
+        <v>0.3125</v>
+      </c>
+      <c r="Z206" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="AA206" s="8">
+        <v>6.2404750000000009</v>
+      </c>
+      <c r="AB206" s="8">
+        <v>15.88125</v>
+      </c>
+      <c r="AC206" s="8">
+        <v>22.407291000000001</v>
+      </c>
+      <c r="AD206" s="8">
+        <v>29.335418749999999</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>0.125</v>
+      </c>
       <c r="AF206" s="9"/>
-      <c r="AG206" s="5"/>
+      <c r="AG206" s="5">
+        <v>-135.69999999999999</v>
+      </c>
       <c r="AH206" s="10">
         <v>2</v>
       </c>
